--- a/excel/compras.xlsx
+++ b/excel/compras.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\progs\BI\BI_Farmacias\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1507B27E-C522-4766-8798-B4B62D956F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31D4638-E0C5-4D79-8E6C-848AA5D8C964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="0" windowWidth="21375" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29730" yWindow="0" windowWidth="21720" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Compras_2025_2026" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16785" uniqueCount="3003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16785" uniqueCount="3011">
   <si>
     <t>id_compra</t>
   </si>
@@ -9033,6 +9033,30 @@
   </si>
   <si>
     <t>Variación vs mismo mes año anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VALLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORTE </t>
+  </si>
+  <si>
+    <t>CENTRRO</t>
+  </si>
+  <si>
+    <t>NOREE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CENTRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NORTE</t>
+  </si>
+  <si>
+    <t>SUUR</t>
+  </si>
+  <si>
+    <t>VAALLE</t>
   </si>
 </sst>
 </file>
@@ -10921,7 +10945,7 @@
         <v>586.29</v>
       </c>
       <c r="X8" t="s">
-        <v>76</v>
+        <v>3003</v>
       </c>
       <c r="Y8" t="s">
         <v>77</v>
@@ -11010,7 +11034,7 @@
         <v>293.5</v>
       </c>
       <c r="X9" t="s">
-        <v>92</v>
+        <v>3004</v>
       </c>
       <c r="Y9" t="s">
         <v>93</v>
@@ -11099,7 +11123,7 @@
         <v>140.55000000000001</v>
       </c>
       <c r="X10" t="s">
-        <v>42</v>
+        <v>3005</v>
       </c>
       <c r="Y10" t="s">
         <v>43</v>
@@ -12167,7 +12191,7 @@
         <v>366.69</v>
       </c>
       <c r="X22" t="s">
-        <v>42</v>
+        <v>3007</v>
       </c>
       <c r="Y22" t="s">
         <v>43</v>
@@ -12434,7 +12458,7 @@
         <v>657.75</v>
       </c>
       <c r="X25" t="s">
-        <v>92</v>
+        <v>3008</v>
       </c>
       <c r="Y25" t="s">
         <v>93</v>
@@ -12612,7 +12636,7 @@
         <v>478.09</v>
       </c>
       <c r="X27" t="s">
-        <v>60</v>
+        <v>3009</v>
       </c>
       <c r="Y27" t="s">
         <v>61</v>
@@ -12701,7 +12725,7 @@
         <v>301.88</v>
       </c>
       <c r="X28" t="s">
-        <v>76</v>
+        <v>3010</v>
       </c>
       <c r="Y28" t="s">
         <v>77</v>
@@ -86749,7 +86773,7 @@
         <v>683.3</v>
       </c>
       <c r="X860" t="s">
-        <v>92</v>
+        <v>3006</v>
       </c>
       <c r="Y860" t="s">
         <v>93</v>

--- a/excel/compras.xlsx
+++ b/excel/compras.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\progs\BI\BI_Farmacias\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995D249E-B5AA-4C17-A1F7-3D52B7F7D91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5E3A4F-AC0C-424D-972E-DA090193DCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29730" yWindow="0" windowWidth="21720" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21720" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Compras_2025_2026" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16785" uniqueCount="3011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16785" uniqueCount="3014">
   <si>
     <t>id_compra</t>
   </si>
@@ -9057,6 +9057,15 @@
   </si>
   <si>
     <t>VAALLE</t>
+  </si>
+  <si>
+    <t>PARCIAL</t>
+  </si>
+  <si>
+    <t>RECHAZADO</t>
+  </si>
+  <si>
+    <t>CANCELADO</t>
   </si>
 </sst>
 </file>
@@ -11235,7 +11244,7 @@
         <v>45670</v>
       </c>
       <c r="AB11" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC11" t="s">
         <v>46</v>
@@ -11324,7 +11333,7 @@
         <v>45671</v>
       </c>
       <c r="AB12" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC12" t="s">
         <v>46</v>
@@ -11591,7 +11600,7 @@
         <v>45673</v>
       </c>
       <c r="AB15" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC15" t="s">
         <v>46</v>
@@ -11947,7 +11956,7 @@
         <v>45678</v>
       </c>
       <c r="AB19" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC19" t="s">
         <v>46</v>
@@ -12125,7 +12134,7 @@
         <v>45678</v>
       </c>
       <c r="AB21" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC21" t="s">
         <v>46</v>
@@ -12214,7 +12223,7 @@
         <v>45676</v>
       </c>
       <c r="AB22" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC22" t="s">
         <v>46</v>
@@ -12303,7 +12312,7 @@
         <v>45682</v>
       </c>
       <c r="AB23" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC23" t="s">
         <v>46</v>
@@ -12570,7 +12579,7 @@
         <v>45683</v>
       </c>
       <c r="AB26" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC26" t="s">
         <v>46</v>
@@ -12837,7 +12846,7 @@
         <v>45687</v>
       </c>
       <c r="AB29" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC29" t="s">
         <v>46</v>
@@ -12926,7 +12935,7 @@
         <v>45683</v>
       </c>
       <c r="AB30" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC30" t="s">
         <v>46</v>
@@ -13193,7 +13202,7 @@
         <v>45688</v>
       </c>
       <c r="AB33" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC33" t="s">
         <v>46</v>
@@ -13549,7 +13558,7 @@
         <v>45691</v>
       </c>
       <c r="AB37" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC37" t="s">
         <v>46</v>
@@ -13727,7 +13736,7 @@
         <v>45695</v>
       </c>
       <c r="AB39" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC39" t="s">
         <v>46</v>
@@ -13816,7 +13825,7 @@
         <v>45691</v>
       </c>
       <c r="AB40" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC40" t="s">
         <v>46</v>
@@ -13905,7 +13914,7 @@
         <v>45697</v>
       </c>
       <c r="AB41" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC41" t="s">
         <v>46</v>
@@ -14172,7 +14181,7 @@
         <v>45694</v>
       </c>
       <c r="AB44" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC44" t="s">
         <v>46</v>
@@ -14261,7 +14270,7 @@
         <v>45700</v>
       </c>
       <c r="AB45" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC45" t="s">
         <v>46</v>
@@ -14350,7 +14359,7 @@
         <v>45700</v>
       </c>
       <c r="AB46" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC46" t="s">
         <v>46</v>
@@ -14617,7 +14626,7 @@
         <v>45701</v>
       </c>
       <c r="AB49" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC49" t="s">
         <v>46</v>
@@ -14973,7 +14982,7 @@
         <v>45705</v>
       </c>
       <c r="AB53" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC53" t="s">
         <v>46</v>
@@ -15151,7 +15160,7 @@
         <v>45706</v>
       </c>
       <c r="AB55" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC55" t="s">
         <v>46</v>
@@ -15240,7 +15249,7 @@
         <v>45704</v>
       </c>
       <c r="AB56" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC56" t="s">
         <v>46</v>
@@ -15329,7 +15338,7 @@
         <v>45710</v>
       </c>
       <c r="AB57" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC57" t="s">
         <v>46</v>
@@ -15596,7 +15605,7 @@
         <v>45711</v>
       </c>
       <c r="AB60" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC60" t="s">
         <v>46</v>
@@ -16219,7 +16228,7 @@
         <v>45718</v>
       </c>
       <c r="AB67" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC67" t="s">
         <v>46</v>
@@ -16308,7 +16317,7 @@
         <v>45718</v>
       </c>
       <c r="AB68" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC68" t="s">
         <v>46</v>
@@ -16575,7 +16584,7 @@
         <v>45720</v>
       </c>
       <c r="AB71" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC71" t="s">
         <v>46</v>
@@ -16931,7 +16940,7 @@
         <v>45721</v>
       </c>
       <c r="AB75" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC75" t="s">
         <v>46</v>
@@ -17109,7 +17118,7 @@
         <v>45726</v>
       </c>
       <c r="AB77" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC77" t="s">
         <v>46</v>
@@ -17198,7 +17207,7 @@
         <v>45722</v>
       </c>
       <c r="AB78" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC78" t="s">
         <v>46</v>
@@ -17287,7 +17296,7 @@
         <v>45728</v>
       </c>
       <c r="AB79" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC79" t="s">
         <v>46</v>
@@ -17554,7 +17563,7 @@
         <v>45725</v>
       </c>
       <c r="AB82" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC82" t="s">
         <v>46</v>
@@ -18711,7 +18720,7 @@
         <v>45741</v>
       </c>
       <c r="AB95" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC95" t="s">
         <v>46</v>
@@ -18800,7 +18809,7 @@
         <v>45741</v>
       </c>
       <c r="AB96" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC96" t="s">
         <v>46</v>
@@ -19067,7 +19076,7 @@
         <v>45741</v>
       </c>
       <c r="AB99" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC99" t="s">
         <v>46</v>
@@ -19423,7 +19432,7 @@
         <v>45746</v>
       </c>
       <c r="AB103" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC103" t="s">
         <v>46</v>
@@ -19601,7 +19610,7 @@
         <v>45746</v>
       </c>
       <c r="AB105" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC105" t="s">
         <v>46</v>
@@ -19690,7 +19699,7 @@
         <v>45749</v>
       </c>
       <c r="AB106" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC106" t="s">
         <v>46</v>
@@ -19779,7 +19788,7 @@
         <v>45749</v>
       </c>
       <c r="AB107" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC107" t="s">
         <v>46</v>
@@ -20046,7 +20055,7 @@
         <v>45749</v>
       </c>
       <c r="AB110" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC110" t="s">
         <v>46</v>
@@ -22182,7 +22191,7 @@
         <v>45773</v>
       </c>
       <c r="AB134" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC134" t="s">
         <v>46</v>
@@ -22271,7 +22280,7 @@
         <v>45771</v>
       </c>
       <c r="AB135" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC135" t="s">
         <v>46</v>
@@ -22538,7 +22547,7 @@
         <v>45776</v>
       </c>
       <c r="AB138" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC138" t="s">
         <v>46</v>
@@ -22894,7 +22903,7 @@
         <v>45775</v>
       </c>
       <c r="AB142" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC142" t="s">
         <v>46</v>
@@ -23072,7 +23081,7 @@
         <v>45781</v>
       </c>
       <c r="AB144" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC144" t="s">
         <v>46</v>
@@ -23161,7 +23170,7 @@
         <v>45781</v>
       </c>
       <c r="AB145" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC145" t="s">
         <v>46</v>
@@ -23250,7 +23259,7 @@
         <v>45779</v>
       </c>
       <c r="AB146" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC146" t="s">
         <v>46</v>
@@ -23517,7 +23526,7 @@
         <v>45787</v>
       </c>
       <c r="AB149" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC149" t="s">
         <v>46</v>
@@ -25653,7 +25662,7 @@
         <v>45805</v>
       </c>
       <c r="AB173" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC173" t="s">
         <v>46</v>
@@ -25742,7 +25751,7 @@
         <v>45803</v>
       </c>
       <c r="AB174" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC174" t="s">
         <v>46</v>
@@ -26009,7 +26018,7 @@
         <v>45808</v>
       </c>
       <c r="AB177" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC177" t="s">
         <v>46</v>
@@ -26365,7 +26374,7 @@
         <v>45810</v>
       </c>
       <c r="AB181" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC181" t="s">
         <v>46</v>
@@ -26543,7 +26552,7 @@
         <v>45813</v>
       </c>
       <c r="AB183" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC183" t="s">
         <v>46</v>
@@ -26632,7 +26641,7 @@
         <v>45811</v>
       </c>
       <c r="AB184" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC184" t="s">
         <v>46</v>
@@ -26721,7 +26730,7 @@
         <v>45817</v>
       </c>
       <c r="AB185" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC185" t="s">
         <v>46</v>
@@ -26988,7 +26997,7 @@
         <v>45818</v>
       </c>
       <c r="AB188" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC188" t="s">
         <v>46</v>
@@ -29124,7 +29133,7 @@
         <v>45834</v>
       </c>
       <c r="AB212" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC212" t="s">
         <v>46</v>
@@ -29213,7 +29222,7 @@
         <v>45840</v>
       </c>
       <c r="AB213" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC213" t="s">
         <v>46</v>
@@ -29480,7 +29489,7 @@
         <v>45838</v>
       </c>
       <c r="AB216" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC216" t="s">
         <v>46</v>
@@ -29836,7 +29845,7 @@
         <v>45845</v>
       </c>
       <c r="AB220" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC220" t="s">
         <v>46</v>
@@ -30014,7 +30023,7 @@
         <v>45846</v>
       </c>
       <c r="AB222" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC222" t="s">
         <v>46</v>
@@ -30103,7 +30112,7 @@
         <v>45848</v>
       </c>
       <c r="AB223" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC223" t="s">
         <v>46</v>
@@ -30192,7 +30201,7 @@
         <v>45848</v>
       </c>
       <c r="AB224" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC224" t="s">
         <v>46</v>
@@ -30459,7 +30468,7 @@
         <v>45850</v>
       </c>
       <c r="AB227" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC227" t="s">
         <v>46</v>
@@ -32595,7 +32604,7 @@
         <v>45872</v>
       </c>
       <c r="AB251" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC251" t="s">
         <v>46</v>
@@ -32684,7 +32693,7 @@
         <v>45868</v>
       </c>
       <c r="AB252" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC252" t="s">
         <v>46</v>
@@ -32951,7 +32960,7 @@
         <v>45873</v>
       </c>
       <c r="AB255" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC255" t="s">
         <v>46</v>
@@ -33307,7 +33316,7 @@
         <v>45876</v>
       </c>
       <c r="AB259" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC259" t="s">
         <v>46</v>
@@ -33485,7 +33494,7 @@
         <v>45880</v>
       </c>
       <c r="AB261" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC261" t="s">
         <v>46</v>
@@ -33574,7 +33583,7 @@
         <v>45880</v>
       </c>
       <c r="AB262" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC262" t="s">
         <v>46</v>
@@ -33663,7 +33672,7 @@
         <v>45882</v>
       </c>
       <c r="AB263" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC263" t="s">
         <v>46</v>
@@ -33930,7 +33939,7 @@
         <v>45879</v>
       </c>
       <c r="AB266" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC266" t="s">
         <v>46</v>
@@ -36066,7 +36075,7 @@
         <v>45903</v>
       </c>
       <c r="AB290" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC290" t="s">
         <v>46</v>
@@ -36155,7 +36164,7 @@
         <v>45903</v>
       </c>
       <c r="AB291" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC291" t="s">
         <v>46</v>
@@ -36422,7 +36431,7 @@
         <v>45906</v>
       </c>
       <c r="AB294" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC294" t="s">
         <v>46</v>
@@ -36778,7 +36787,7 @@
         <v>45906</v>
       </c>
       <c r="AB298" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC298" t="s">
         <v>46</v>
@@ -36956,7 +36965,7 @@
         <v>45908</v>
       </c>
       <c r="AB300" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC300" t="s">
         <v>46</v>
@@ -37045,7 +37054,7 @@
         <v>45913</v>
       </c>
       <c r="AB301" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC301" t="s">
         <v>46</v>
@@ -37134,7 +37143,7 @@
         <v>45913</v>
       </c>
       <c r="AB302" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC302" t="s">
         <v>46</v>
@@ -37401,7 +37410,7 @@
         <v>45917</v>
       </c>
       <c r="AB305" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC305" t="s">
         <v>46</v>
@@ -39537,7 +39546,7 @@
         <v>45935</v>
       </c>
       <c r="AB329" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC329" t="s">
         <v>46</v>
@@ -39626,7 +39635,7 @@
         <v>45933</v>
       </c>
       <c r="AB330" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC330" t="s">
         <v>46</v>
@@ -39893,7 +39902,7 @@
         <v>45941</v>
       </c>
       <c r="AB333" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC333" t="s">
         <v>46</v>
@@ -40249,7 +40258,7 @@
         <v>45944</v>
       </c>
       <c r="AB337" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC337" t="s">
         <v>46</v>
@@ -40427,7 +40436,7 @@
         <v>45944</v>
       </c>
       <c r="AB339" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC339" t="s">
         <v>46</v>
@@ -40516,7 +40525,7 @@
         <v>45942</v>
       </c>
       <c r="AB340" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC340" t="s">
         <v>46</v>
@@ -40605,7 +40614,7 @@
         <v>45945</v>
       </c>
       <c r="AB341" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC341" t="s">
         <v>46</v>
@@ -40872,7 +40881,7 @@
         <v>45949</v>
       </c>
       <c r="AB344" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC344" t="s">
         <v>46</v>
@@ -43008,7 +43017,7 @@
         <v>45965</v>
       </c>
       <c r="AB368" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC368" t="s">
         <v>46</v>
@@ -43097,7 +43106,7 @@
         <v>45971</v>
       </c>
       <c r="AB369" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC369" t="s">
         <v>46</v>
@@ -43364,7 +43373,7 @@
         <v>45972</v>
       </c>
       <c r="AB372" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC372" t="s">
         <v>46</v>
@@ -43720,7 +43729,7 @@
         <v>45972</v>
       </c>
       <c r="AB376" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC376" t="s">
         <v>46</v>
@@ -43898,7 +43907,7 @@
         <v>45977</v>
       </c>
       <c r="AB378" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC378" t="s">
         <v>46</v>
@@ -43987,7 +43996,7 @@
         <v>45977</v>
       </c>
       <c r="AB379" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC379" t="s">
         <v>46</v>
@@ -44076,7 +44085,7 @@
         <v>45975</v>
       </c>
       <c r="AB380" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC380" t="s">
         <v>46</v>
@@ -44343,7 +44352,7 @@
         <v>45980</v>
       </c>
       <c r="AB383" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC383" t="s">
         <v>46</v>
@@ -46479,7 +46488,7 @@
         <v>46002</v>
       </c>
       <c r="AB407" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC407" t="s">
         <v>46</v>
@@ -46568,7 +46577,7 @@
         <v>46002</v>
       </c>
       <c r="AB408" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC408" t="s">
         <v>46</v>
@@ -46835,7 +46844,7 @@
         <v>46002</v>
       </c>
       <c r="AB411" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC411" t="s">
         <v>46</v>
@@ -47191,7 +47200,7 @@
         <v>46007</v>
       </c>
       <c r="AB415" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC415" t="s">
         <v>46</v>
@@ -47369,7 +47378,7 @@
         <v>46007</v>
       </c>
       <c r="AB417" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC417" t="s">
         <v>46</v>
@@ -47458,7 +47467,7 @@
         <v>46006</v>
       </c>
       <c r="AB418" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC418" t="s">
         <v>46</v>
@@ -47547,7 +47556,7 @@
         <v>46012</v>
       </c>
       <c r="AB419" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC419" t="s">
         <v>46</v>
@@ -47814,7 +47823,7 @@
         <v>46010</v>
       </c>
       <c r="AB422" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC422" t="s">
         <v>46</v>
@@ -49950,7 +49959,7 @@
         <v>46034</v>
       </c>
       <c r="AB446" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC446" t="s">
         <v>46</v>
@@ -50039,7 +50048,7 @@
         <v>46034</v>
       </c>
       <c r="AB447" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC447" t="s">
         <v>46</v>
@@ -50306,7 +50315,7 @@
         <v>46033</v>
       </c>
       <c r="AB450" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC450" t="s">
         <v>46</v>
@@ -50662,7 +50671,7 @@
         <v>46037</v>
       </c>
       <c r="AB454" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC454" t="s">
         <v>46</v>
@@ -50840,7 +50849,7 @@
         <v>46038</v>
       </c>
       <c r="AB456" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC456" t="s">
         <v>46</v>
@@ -50929,7 +50938,7 @@
         <v>46044</v>
       </c>
       <c r="AB457" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC457" t="s">
         <v>46</v>
@@ -51018,7 +51027,7 @@
         <v>46044</v>
       </c>
       <c r="AB458" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC458" t="s">
         <v>46</v>
@@ -51285,7 +51294,7 @@
         <v>46044</v>
       </c>
       <c r="AB461" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC461" t="s">
         <v>46</v>
@@ -53421,7 +53430,7 @@
         <v>46064</v>
       </c>
       <c r="AB485" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC485" t="s">
         <v>46</v>
@@ -53510,7 +53519,7 @@
         <v>46067</v>
       </c>
       <c r="AB486" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC486" t="s">
         <v>46</v>
@@ -53777,7 +53786,7 @@
         <v>46071</v>
       </c>
       <c r="AB489" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC489" t="s">
         <v>46</v>
@@ -54133,7 +54142,7 @@
         <v>46074</v>
       </c>
       <c r="AB493" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC493" t="s">
         <v>46</v>
@@ -54311,7 +54320,7 @@
         <v>46076</v>
       </c>
       <c r="AB495" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC495" t="s">
         <v>46</v>
@@ -54400,7 +54409,7 @@
         <v>46076</v>
       </c>
       <c r="AB496" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC496" t="s">
         <v>46</v>
@@ -54489,7 +54498,7 @@
         <v>46074</v>
       </c>
       <c r="AB497" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC497" t="s">
         <v>46</v>
@@ -54756,7 +54765,7 @@
         <v>46079</v>
       </c>
       <c r="AB500" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC500" t="s">
         <v>46</v>
@@ -56892,7 +56901,7 @@
         <v>46095</v>
       </c>
       <c r="AB524" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC524" t="s">
         <v>46</v>
@@ -56981,7 +56990,7 @@
         <v>46098</v>
       </c>
       <c r="AB525" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC525" t="s">
         <v>46</v>
@@ -57248,7 +57257,7 @@
         <v>46102</v>
       </c>
       <c r="AB528" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC528" t="s">
         <v>46</v>
@@ -57604,7 +57613,7 @@
         <v>46101</v>
       </c>
       <c r="AB532" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC532" t="s">
         <v>46</v>
@@ -57782,7 +57791,7 @@
         <v>46107</v>
       </c>
       <c r="AB534" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC534" t="s">
         <v>46</v>
@@ -57871,7 +57880,7 @@
         <v>46107</v>
       </c>
       <c r="AB535" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC535" t="s">
         <v>46</v>
@@ -57960,7 +57969,7 @@
         <v>46108</v>
       </c>
       <c r="AB536" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC536" t="s">
         <v>46</v>
@@ -58227,7 +58236,7 @@
         <v>46110</v>
       </c>
       <c r="AB539" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC539" t="s">
         <v>46</v>
@@ -63834,7 +63843,7 @@
         <v>46160</v>
       </c>
       <c r="AB602" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC602" t="s">
         <v>46</v>
@@ -63923,7 +63932,7 @@
         <v>46166</v>
       </c>
       <c r="AB603" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC603" t="s">
         <v>46</v>
@@ -64190,7 +64199,7 @@
         <v>46167</v>
       </c>
       <c r="AB606" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC606" t="s">
         <v>46</v>
@@ -64546,7 +64555,7 @@
         <v>46171</v>
       </c>
       <c r="AB610" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC610" t="s">
         <v>46</v>
@@ -64724,7 +64733,7 @@
         <v>46172</v>
       </c>
       <c r="AB612" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC612" t="s">
         <v>46</v>
@@ -64813,7 +64822,7 @@
         <v>46174</v>
       </c>
       <c r="AB613" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC613" t="s">
         <v>46</v>
@@ -64902,7 +64911,7 @@
         <v>46174</v>
       </c>
       <c r="AB614" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC614" t="s">
         <v>46</v>
@@ -65169,7 +65178,7 @@
         <v>46176</v>
       </c>
       <c r="AB617" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC617" t="s">
         <v>46</v>
@@ -70776,7 +70785,7 @@
         <v>46229</v>
       </c>
       <c r="AB680" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC680" t="s">
         <v>46</v>
@@ -70865,7 +70874,7 @@
         <v>46229</v>
       </c>
       <c r="AB681" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC681" t="s">
         <v>46</v>
@@ -71132,7 +71141,7 @@
         <v>46232</v>
       </c>
       <c r="AB684" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC684" t="s">
         <v>46</v>
@@ -71488,7 +71497,7 @@
         <v>46232</v>
       </c>
       <c r="AB688" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC688" t="s">
         <v>46</v>
@@ -71666,7 +71675,7 @@
         <v>46237</v>
       </c>
       <c r="AB690" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC690" t="s">
         <v>46</v>
@@ -71755,7 +71764,7 @@
         <v>46237</v>
       </c>
       <c r="AB691" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC691" t="s">
         <v>46</v>
@@ -71844,7 +71853,7 @@
         <v>46235</v>
       </c>
       <c r="AB692" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC692" t="s">
         <v>46</v>
@@ -72111,7 +72120,7 @@
         <v>46239</v>
       </c>
       <c r="AB695" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC695" t="s">
         <v>46</v>
@@ -77718,7 +77727,7 @@
         <v>46290</v>
       </c>
       <c r="AB758" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC758" t="s">
         <v>46</v>
@@ -77807,7 +77816,7 @@
         <v>46296</v>
       </c>
       <c r="AB759" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC759" t="s">
         <v>46</v>
@@ -78074,7 +78083,7 @@
         <v>46293</v>
       </c>
       <c r="AB762" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC762" t="s">
         <v>46</v>
@@ -78430,7 +78439,7 @@
         <v>46301</v>
       </c>
       <c r="AB766" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC766" t="s">
         <v>46</v>
@@ -78608,7 +78617,7 @@
         <v>46299</v>
       </c>
       <c r="AB768" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC768" t="s">
         <v>46</v>
@@ -78697,7 +78706,7 @@
         <v>46305</v>
       </c>
       <c r="AB769" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC769" t="s">
         <v>46</v>
@@ -78786,7 +78795,7 @@
         <v>46305</v>
       </c>
       <c r="AB770" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC770" t="s">
         <v>46</v>
@@ -79053,7 +79062,7 @@
         <v>46306</v>
       </c>
       <c r="AB773" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC773" t="s">
         <v>46</v>
@@ -84660,7 +84669,7 @@
         <v>46360</v>
       </c>
       <c r="AB836" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC836" t="s">
         <v>46</v>
@@ -84749,7 +84758,7 @@
         <v>46358</v>
       </c>
       <c r="AB837" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC837" t="s">
         <v>46</v>
@@ -85016,7 +85025,7 @@
         <v>46359</v>
       </c>
       <c r="AB840" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC840" t="s">
         <v>46</v>
@@ -85372,7 +85381,7 @@
         <v>46362</v>
       </c>
       <c r="AB844" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC844" t="s">
         <v>46</v>
@@ -85550,7 +85559,7 @@
         <v>46368</v>
       </c>
       <c r="AB846" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC846" t="s">
         <v>46</v>
@@ -85639,7 +85648,7 @@
         <v>46368</v>
       </c>
       <c r="AB847" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC847" t="s">
         <v>46</v>
@@ -85728,7 +85737,7 @@
         <v>46366</v>
       </c>
       <c r="AB848" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC848" t="s">
         <v>46</v>
@@ -85995,7 +86004,7 @@
         <v>46373</v>
       </c>
       <c r="AB851" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC851" t="s">
         <v>46</v>

--- a/excel/compras.xlsx
+++ b/excel/compras.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\progs\BI\BI_Farmacias\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5E3A4F-AC0C-424D-972E-DA090193DCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E38896-50A4-4F0C-AC51-2A7F58AA392A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21720" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="0" windowWidth="21720" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Compras_2025_2026" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16785" uniqueCount="3014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16785" uniqueCount="3015">
   <si>
     <t>id_compra</t>
   </si>
@@ -9066,6 +9066,9 @@
   </si>
   <si>
     <t>CANCELADO</t>
+  </si>
+  <si>
+    <t>Farmacia Valle de Cumbayá</t>
   </si>
 </sst>
 </file>
@@ -9990,6 +9993,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tbl_compras" displayName="tbl_compras" ref="A1:AC875">
+  <autoFilter ref="A1:AC875" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="1">
+      <filters>
+        <dateGroupItem year="2026" dateTimeGrouping="year"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="24">
+      <filters>
+        <filter val="Farmacia Centro Histórico"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="29">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id_compra"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="fecha_compra" dataDxfId="2"/>
@@ -10264,7 +10279,7 @@
     <col min="22" max="22" width="15.625" customWidth="1"/>
     <col min="23" max="23" width="11.25" customWidth="1"/>
     <col min="24" max="24" width="21.875" customWidth="1"/>
-    <col min="25" max="25" width="24" customWidth="1"/>
+    <col min="25" max="25" width="32.875" customWidth="1"/>
     <col min="26" max="26" width="15.375" customWidth="1"/>
     <col min="27" max="27" width="21.875" customWidth="1"/>
     <col min="28" max="28" width="16.5" customWidth="1"/>
@@ -10360,7 +10375,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:29" hidden="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -10449,7 +10464,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:29" hidden="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -10538,7 +10553,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4" spans="1:29" hidden="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -10612,7 +10627,7 @@
         <v>76</v>
       </c>
       <c r="Y4" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z4" t="s">
         <v>78</v>
@@ -10627,7 +10642,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5" spans="1:29" hidden="1">
       <c r="A5">
         <v>4</v>
       </c>
@@ -10716,7 +10731,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6" spans="1:29" hidden="1">
       <c r="A6">
         <v>5</v>
       </c>
@@ -10805,7 +10820,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7" spans="1:29" hidden="1">
       <c r="A7">
         <v>6</v>
       </c>
@@ -10894,7 +10909,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8" spans="1:29" hidden="1">
       <c r="A8">
         <v>7</v>
       </c>
@@ -10968,7 +10983,7 @@
         <v>3003</v>
       </c>
       <c r="Y8" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z8" t="s">
         <v>78</v>
@@ -10983,7 +10998,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:29">
+    <row r="9" spans="1:29" hidden="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -11072,7 +11087,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:29">
+    <row r="10" spans="1:29" hidden="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -11155,13 +11170,13 @@
         <v>45670</v>
       </c>
       <c r="AB10" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11" spans="1:29" hidden="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -11250,7 +11265,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12" spans="1:29" hidden="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -11339,7 +11354,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13" spans="1:29" hidden="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -11428,7 +11443,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:29" hidden="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -11517,7 +11532,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:29" hidden="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -11606,7 +11621,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:29">
+    <row r="16" spans="1:29" hidden="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -11680,7 +11695,7 @@
         <v>76</v>
       </c>
       <c r="Y16" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z16" t="s">
         <v>78</v>
@@ -11695,7 +11710,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:29">
+    <row r="17" spans="1:29" hidden="1">
       <c r="A17">
         <v>16</v>
       </c>
@@ -11784,7 +11799,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:29">
+    <row r="18" spans="1:29" hidden="1">
       <c r="A18">
         <v>17</v>
       </c>
@@ -11873,7 +11888,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:29">
+    <row r="19" spans="1:29" hidden="1">
       <c r="A19">
         <v>18</v>
       </c>
@@ -11962,7 +11977,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:29">
+    <row r="20" spans="1:29" hidden="1">
       <c r="A20">
         <v>19</v>
       </c>
@@ -12036,7 +12051,7 @@
         <v>76</v>
       </c>
       <c r="Y20" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z20" t="s">
         <v>78</v>
@@ -12051,7 +12066,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:29">
+    <row r="21" spans="1:29" hidden="1">
       <c r="A21">
         <v>20</v>
       </c>
@@ -12140,7 +12155,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:29">
+    <row r="22" spans="1:29" hidden="1">
       <c r="A22">
         <v>21</v>
       </c>
@@ -12229,7 +12244,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:29">
+    <row r="23" spans="1:29" hidden="1">
       <c r="A23">
         <v>22</v>
       </c>
@@ -12318,7 +12333,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:29">
+    <row r="24" spans="1:29" hidden="1">
       <c r="A24">
         <v>23</v>
       </c>
@@ -12407,7 +12422,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:29">
+    <row r="25" spans="1:29" hidden="1">
       <c r="A25">
         <v>24</v>
       </c>
@@ -12496,7 +12511,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:29">
+    <row r="26" spans="1:29" hidden="1">
       <c r="A26">
         <v>25</v>
       </c>
@@ -12585,7 +12600,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:29">
+    <row r="27" spans="1:29" hidden="1">
       <c r="A27">
         <v>26</v>
       </c>
@@ -12674,7 +12689,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:29">
+    <row r="28" spans="1:29" hidden="1">
       <c r="A28">
         <v>27</v>
       </c>
@@ -12748,7 +12763,7 @@
         <v>3010</v>
       </c>
       <c r="Y28" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z28" t="s">
         <v>78</v>
@@ -12763,7 +12778,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:29">
+    <row r="29" spans="1:29" hidden="1">
       <c r="A29">
         <v>28</v>
       </c>
@@ -12852,7 +12867,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:29">
+    <row r="30" spans="1:29" hidden="1">
       <c r="A30">
         <v>29</v>
       </c>
@@ -12941,7 +12956,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:29">
+    <row r="31" spans="1:29" hidden="1">
       <c r="A31">
         <v>30</v>
       </c>
@@ -13030,7 +13045,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:29">
+    <row r="32" spans="1:29" hidden="1">
       <c r="A32">
         <v>31</v>
       </c>
@@ -13104,7 +13119,7 @@
         <v>76</v>
       </c>
       <c r="Y32" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z32" t="s">
         <v>78</v>
@@ -13119,7 +13134,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:29">
+    <row r="33" spans="1:29" hidden="1">
       <c r="A33">
         <v>32</v>
       </c>
@@ -13208,7 +13223,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:29">
+    <row r="34" spans="1:29" hidden="1">
       <c r="A34">
         <v>33</v>
       </c>
@@ -13297,7 +13312,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:29">
+    <row r="35" spans="1:29" hidden="1">
       <c r="A35">
         <v>34</v>
       </c>
@@ -13386,7 +13401,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:29">
+    <row r="36" spans="1:29" hidden="1">
       <c r="A36">
         <v>35</v>
       </c>
@@ -13475,7 +13490,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:29">
+    <row r="37" spans="1:29" hidden="1">
       <c r="A37">
         <v>36</v>
       </c>
@@ -13564,7 +13579,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:29">
+    <row r="38" spans="1:29" hidden="1">
       <c r="A38">
         <v>37</v>
       </c>
@@ -13653,7 +13668,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:29">
+    <row r="39" spans="1:29" hidden="1">
       <c r="A39">
         <v>38</v>
       </c>
@@ -13742,7 +13757,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:29">
+    <row r="40" spans="1:29" hidden="1">
       <c r="A40">
         <v>39</v>
       </c>
@@ -13816,7 +13831,7 @@
         <v>76</v>
       </c>
       <c r="Y40" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z40" t="s">
         <v>78</v>
@@ -13831,7 +13846,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:29">
+    <row r="41" spans="1:29" hidden="1">
       <c r="A41">
         <v>40</v>
       </c>
@@ -13920,7 +13935,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:29">
+    <row r="42" spans="1:29" hidden="1">
       <c r="A42">
         <v>41</v>
       </c>
@@ -14009,7 +14024,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:29">
+    <row r="43" spans="1:29" hidden="1">
       <c r="A43">
         <v>42</v>
       </c>
@@ -14098,7 +14113,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:29">
+    <row r="44" spans="1:29" hidden="1">
       <c r="A44">
         <v>43</v>
       </c>
@@ -14172,7 +14187,7 @@
         <v>76</v>
       </c>
       <c r="Y44" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z44" t="s">
         <v>78</v>
@@ -14187,7 +14202,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:29">
+    <row r="45" spans="1:29" hidden="1">
       <c r="A45">
         <v>44</v>
       </c>
@@ -14276,7 +14291,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:29">
+    <row r="46" spans="1:29" hidden="1">
       <c r="A46">
         <v>45</v>
       </c>
@@ -14365,7 +14380,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:29">
+    <row r="47" spans="1:29" hidden="1">
       <c r="A47">
         <v>46</v>
       </c>
@@ -14454,7 +14469,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:29">
+    <row r="48" spans="1:29" hidden="1">
       <c r="A48">
         <v>47</v>
       </c>
@@ -14543,7 +14558,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:29">
+    <row r="49" spans="1:29" hidden="1">
       <c r="A49">
         <v>48</v>
       </c>
@@ -14632,7 +14647,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:29">
+    <row r="50" spans="1:29" hidden="1">
       <c r="A50">
         <v>49</v>
       </c>
@@ -14721,7 +14736,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:29">
+    <row r="51" spans="1:29" hidden="1">
       <c r="A51">
         <v>50</v>
       </c>
@@ -14810,7 +14825,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:29">
+    <row r="52" spans="1:29" hidden="1">
       <c r="A52">
         <v>51</v>
       </c>
@@ -14884,7 +14899,7 @@
         <v>76</v>
       </c>
       <c r="Y52" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z52" t="s">
         <v>78</v>
@@ -14899,7 +14914,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:29">
+    <row r="53" spans="1:29" hidden="1">
       <c r="A53">
         <v>52</v>
       </c>
@@ -14988,7 +15003,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:29">
+    <row r="54" spans="1:29" hidden="1">
       <c r="A54">
         <v>53</v>
       </c>
@@ -15077,7 +15092,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:29">
+    <row r="55" spans="1:29" hidden="1">
       <c r="A55">
         <v>54</v>
       </c>
@@ -15166,7 +15181,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:29">
+    <row r="56" spans="1:29" hidden="1">
       <c r="A56">
         <v>55</v>
       </c>
@@ -15240,7 +15255,7 @@
         <v>76</v>
       </c>
       <c r="Y56" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z56" t="s">
         <v>78</v>
@@ -15255,7 +15270,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:29">
+    <row r="57" spans="1:29" hidden="1">
       <c r="A57">
         <v>56</v>
       </c>
@@ -15344,7 +15359,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:29">
+    <row r="58" spans="1:29" hidden="1">
       <c r="A58">
         <v>57</v>
       </c>
@@ -15427,13 +15442,13 @@
         <v>45710</v>
       </c>
       <c r="AB58" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC58" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:29">
+    <row r="59" spans="1:29" hidden="1">
       <c r="A59">
         <v>58</v>
       </c>
@@ -15516,13 +15531,13 @@
         <v>45710</v>
       </c>
       <c r="AB59" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC59" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:29">
+    <row r="60" spans="1:29" hidden="1">
       <c r="A60">
         <v>59</v>
       </c>
@@ -15611,7 +15626,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61" spans="1:29">
+    <row r="61" spans="1:29" hidden="1">
       <c r="A61">
         <v>60</v>
       </c>
@@ -15700,7 +15715,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:29">
+    <row r="62" spans="1:29" hidden="1">
       <c r="A62">
         <v>61</v>
       </c>
@@ -15789,7 +15804,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="63" spans="1:29">
+    <row r="63" spans="1:29" hidden="1">
       <c r="A63">
         <v>62</v>
       </c>
@@ -15878,7 +15893,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:29">
+    <row r="64" spans="1:29" hidden="1">
       <c r="A64">
         <v>63</v>
       </c>
@@ -15952,7 +15967,7 @@
         <v>76</v>
       </c>
       <c r="Y64" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z64" t="s">
         <v>78</v>
@@ -15967,7 +15982,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:29">
+    <row r="65" spans="1:29" hidden="1">
       <c r="A65">
         <v>64</v>
       </c>
@@ -16056,7 +16071,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:29">
+    <row r="66" spans="1:29" hidden="1">
       <c r="A66">
         <v>65</v>
       </c>
@@ -16145,7 +16160,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:29">
+    <row r="67" spans="1:29" hidden="1">
       <c r="A67">
         <v>66</v>
       </c>
@@ -16234,7 +16249,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:29">
+    <row r="68" spans="1:29" hidden="1">
       <c r="A68">
         <v>67</v>
       </c>
@@ -16308,7 +16323,7 @@
         <v>76</v>
       </c>
       <c r="Y68" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z68" t="s">
         <v>78</v>
@@ -16323,7 +16338,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:29">
+    <row r="69" spans="1:29" hidden="1">
       <c r="A69">
         <v>68</v>
       </c>
@@ -16412,7 +16427,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" spans="1:29">
+    <row r="70" spans="1:29" hidden="1">
       <c r="A70">
         <v>69</v>
       </c>
@@ -16501,7 +16516,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71" spans="1:29">
+    <row r="71" spans="1:29" hidden="1">
       <c r="A71">
         <v>70</v>
       </c>
@@ -16590,7 +16605,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="72" spans="1:29">
+    <row r="72" spans="1:29" hidden="1">
       <c r="A72">
         <v>71</v>
       </c>
@@ -16679,7 +16694,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:29">
+    <row r="73" spans="1:29" hidden="1">
       <c r="A73">
         <v>72</v>
       </c>
@@ -16768,7 +16783,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="74" spans="1:29">
+    <row r="74" spans="1:29" hidden="1">
       <c r="A74">
         <v>73</v>
       </c>
@@ -16857,7 +16872,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="75" spans="1:29">
+    <row r="75" spans="1:29" hidden="1">
       <c r="A75">
         <v>74</v>
       </c>
@@ -16931,7 +16946,7 @@
         <v>76</v>
       </c>
       <c r="Y75" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z75" t="s">
         <v>78</v>
@@ -16946,7 +16961,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="76" spans="1:29">
+    <row r="76" spans="1:29" hidden="1">
       <c r="A76">
         <v>75</v>
       </c>
@@ -17020,7 +17035,7 @@
         <v>76</v>
       </c>
       <c r="Y76" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z76" t="s">
         <v>78</v>
@@ -17035,7 +17050,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="77" spans="1:29">
+    <row r="77" spans="1:29" hidden="1">
       <c r="A77">
         <v>76</v>
       </c>
@@ -17124,7 +17139,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="78" spans="1:29">
+    <row r="78" spans="1:29" hidden="1">
       <c r="A78">
         <v>77</v>
       </c>
@@ -17213,7 +17228,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="79" spans="1:29">
+    <row r="79" spans="1:29" hidden="1">
       <c r="A79">
         <v>78</v>
       </c>
@@ -17302,7 +17317,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="80" spans="1:29">
+    <row r="80" spans="1:29" hidden="1">
       <c r="A80">
         <v>79</v>
       </c>
@@ -17376,7 +17391,7 @@
         <v>76</v>
       </c>
       <c r="Y80" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z80" t="s">
         <v>78</v>
@@ -17391,7 +17406,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="81" spans="1:29">
+    <row r="81" spans="1:29" hidden="1">
       <c r="A81">
         <v>80</v>
       </c>
@@ -17480,7 +17495,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="82" spans="1:29">
+    <row r="82" spans="1:29" hidden="1">
       <c r="A82">
         <v>81</v>
       </c>
@@ -17569,7 +17584,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="83" spans="1:29">
+    <row r="83" spans="1:29" hidden="1">
       <c r="A83">
         <v>82</v>
       </c>
@@ -17658,7 +17673,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="84" spans="1:29">
+    <row r="84" spans="1:29" hidden="1">
       <c r="A84">
         <v>83</v>
       </c>
@@ -17732,7 +17747,7 @@
         <v>76</v>
       </c>
       <c r="Y84" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z84" t="s">
         <v>78</v>
@@ -17747,7 +17762,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="85" spans="1:29">
+    <row r="85" spans="1:29" hidden="1">
       <c r="A85">
         <v>84</v>
       </c>
@@ -17836,7 +17851,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:29">
+    <row r="86" spans="1:29" hidden="1">
       <c r="A86">
         <v>85</v>
       </c>
@@ -17925,7 +17940,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="87" spans="1:29">
+    <row r="87" spans="1:29" hidden="1">
       <c r="A87">
         <v>86</v>
       </c>
@@ -17999,7 +18014,7 @@
         <v>76</v>
       </c>
       <c r="Y87" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z87" t="s">
         <v>78</v>
@@ -18014,7 +18029,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="88" spans="1:29">
+    <row r="88" spans="1:29" hidden="1">
       <c r="A88">
         <v>87</v>
       </c>
@@ -18088,7 +18103,7 @@
         <v>76</v>
       </c>
       <c r="Y88" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z88" t="s">
         <v>78</v>
@@ -18103,7 +18118,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:29">
+    <row r="89" spans="1:29" hidden="1">
       <c r="A89">
         <v>88</v>
       </c>
@@ -18192,7 +18207,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="90" spans="1:29">
+    <row r="90" spans="1:29" hidden="1">
       <c r="A90">
         <v>89</v>
       </c>
@@ -18275,13 +18290,13 @@
         <v>45736</v>
       </c>
       <c r="AB90" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC90" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="91" spans="1:29">
+    <row r="91" spans="1:29" hidden="1">
       <c r="A91">
         <v>90</v>
       </c>
@@ -18364,13 +18379,13 @@
         <v>45736</v>
       </c>
       <c r="AB91" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC91" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="92" spans="1:29">
+    <row r="92" spans="1:29" hidden="1">
       <c r="A92">
         <v>91</v>
       </c>
@@ -18444,7 +18459,7 @@
         <v>76</v>
       </c>
       <c r="Y92" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z92" t="s">
         <v>78</v>
@@ -18453,13 +18468,13 @@
         <v>45734</v>
       </c>
       <c r="AB92" t="s">
-        <v>45</v>
+        <v>3011</v>
       </c>
       <c r="AC92" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="93" spans="1:29">
+    <row r="93" spans="1:29" hidden="1">
       <c r="A93">
         <v>92</v>
       </c>
@@ -18548,7 +18563,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="94" spans="1:29">
+    <row r="94" spans="1:29" hidden="1">
       <c r="A94">
         <v>93</v>
       </c>
@@ -18637,7 +18652,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="95" spans="1:29">
+    <row r="95" spans="1:29" hidden="1">
       <c r="A95">
         <v>94</v>
       </c>
@@ -18726,7 +18741,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="96" spans="1:29">
+    <row r="96" spans="1:29" hidden="1">
       <c r="A96">
         <v>95</v>
       </c>
@@ -18800,7 +18815,7 @@
         <v>76</v>
       </c>
       <c r="Y96" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z96" t="s">
         <v>78</v>
@@ -18815,7 +18830,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:29">
+    <row r="97" spans="1:29" hidden="1">
       <c r="A97">
         <v>96</v>
       </c>
@@ -18904,7 +18919,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="98" spans="1:29">
+    <row r="98" spans="1:29" hidden="1">
       <c r="A98">
         <v>97</v>
       </c>
@@ -18993,7 +19008,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="99" spans="1:29">
+    <row r="99" spans="1:29" hidden="1">
       <c r="A99">
         <v>98</v>
       </c>
@@ -19067,7 +19082,7 @@
         <v>76</v>
       </c>
       <c r="Y99" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z99" t="s">
         <v>78</v>
@@ -19082,7 +19097,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="100" spans="1:29">
+    <row r="100" spans="1:29" hidden="1">
       <c r="A100">
         <v>99</v>
       </c>
@@ -19156,7 +19171,7 @@
         <v>76</v>
       </c>
       <c r="Y100" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z100" t="s">
         <v>78</v>
@@ -19171,7 +19186,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="101" spans="1:29">
+    <row r="101" spans="1:29" hidden="1">
       <c r="A101">
         <v>100</v>
       </c>
@@ -19260,7 +19275,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="102" spans="1:29">
+    <row r="102" spans="1:29" hidden="1">
       <c r="A102">
         <v>101</v>
       </c>
@@ -19349,7 +19364,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="103" spans="1:29">
+    <row r="103" spans="1:29" hidden="1">
       <c r="A103">
         <v>102</v>
       </c>
@@ -19438,7 +19453,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:29">
+    <row r="104" spans="1:29" hidden="1">
       <c r="A104">
         <v>103</v>
       </c>
@@ -19512,7 +19527,7 @@
         <v>76</v>
       </c>
       <c r="Y104" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z104" t="s">
         <v>78</v>
@@ -19527,7 +19542,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="105" spans="1:29">
+    <row r="105" spans="1:29" hidden="1">
       <c r="A105">
         <v>104</v>
       </c>
@@ -19616,7 +19631,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="106" spans="1:29">
+    <row r="106" spans="1:29" hidden="1">
       <c r="A106">
         <v>105</v>
       </c>
@@ -19705,7 +19720,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="107" spans="1:29">
+    <row r="107" spans="1:29" hidden="1">
       <c r="A107">
         <v>106</v>
       </c>
@@ -19794,7 +19809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="108" spans="1:29">
+    <row r="108" spans="1:29" hidden="1">
       <c r="A108">
         <v>107</v>
       </c>
@@ -19868,7 +19883,7 @@
         <v>76</v>
       </c>
       <c r="Y108" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z108" t="s">
         <v>78</v>
@@ -19883,7 +19898,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="109" spans="1:29">
+    <row r="109" spans="1:29" hidden="1">
       <c r="A109">
         <v>108</v>
       </c>
@@ -19972,7 +19987,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="110" spans="1:29">
+    <row r="110" spans="1:29" hidden="1">
       <c r="A110">
         <v>109</v>
       </c>
@@ -20061,7 +20076,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="111" spans="1:29">
+    <row r="111" spans="1:29" hidden="1">
       <c r="A111">
         <v>110</v>
       </c>
@@ -20135,7 +20150,7 @@
         <v>76</v>
       </c>
       <c r="Y111" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z111" t="s">
         <v>78</v>
@@ -20150,7 +20165,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="112" spans="1:29">
+    <row r="112" spans="1:29" hidden="1">
       <c r="A112">
         <v>111</v>
       </c>
@@ -20224,7 +20239,7 @@
         <v>76</v>
       </c>
       <c r="Y112" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z112" t="s">
         <v>78</v>
@@ -20239,7 +20254,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="1:29">
+    <row r="113" spans="1:29" hidden="1">
       <c r="A113">
         <v>112</v>
       </c>
@@ -20328,7 +20343,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="114" spans="1:29">
+    <row r="114" spans="1:29" hidden="1">
       <c r="A114">
         <v>113</v>
       </c>
@@ -20417,7 +20432,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="115" spans="1:29">
+    <row r="115" spans="1:29" hidden="1">
       <c r="A115">
         <v>114</v>
       </c>
@@ -20506,7 +20521,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="116" spans="1:29">
+    <row r="116" spans="1:29" hidden="1">
       <c r="A116">
         <v>115</v>
       </c>
@@ -20580,7 +20595,7 @@
         <v>76</v>
       </c>
       <c r="Y116" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z116" t="s">
         <v>78</v>
@@ -20595,7 +20610,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="117" spans="1:29">
+    <row r="117" spans="1:29" hidden="1">
       <c r="A117">
         <v>116</v>
       </c>
@@ -20678,13 +20693,13 @@
         <v>45756</v>
       </c>
       <c r="AB117" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC117" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="118" spans="1:29">
+    <row r="118" spans="1:29" hidden="1">
       <c r="A118">
         <v>117</v>
       </c>
@@ -20767,13 +20782,13 @@
         <v>45759</v>
       </c>
       <c r="AB118" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC118" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="119" spans="1:29">
+    <row r="119" spans="1:29" hidden="1">
       <c r="A119">
         <v>118</v>
       </c>
@@ -20862,7 +20877,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="120" spans="1:29">
+    <row r="120" spans="1:29" hidden="1">
       <c r="A120">
         <v>119</v>
       </c>
@@ -20936,7 +20951,7 @@
         <v>76</v>
       </c>
       <c r="Y120" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z120" t="s">
         <v>78</v>
@@ -20951,7 +20966,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="121" spans="1:29">
+    <row r="121" spans="1:29" hidden="1">
       <c r="A121">
         <v>120</v>
       </c>
@@ -21040,7 +21055,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="122" spans="1:29">
+    <row r="122" spans="1:29" hidden="1">
       <c r="A122">
         <v>121</v>
       </c>
@@ -21123,13 +21138,13 @@
         <v>45763</v>
       </c>
       <c r="AB122" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC122" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="123" spans="1:29">
+    <row r="123" spans="1:29" hidden="1">
       <c r="A123">
         <v>122</v>
       </c>
@@ -21203,7 +21218,7 @@
         <v>76</v>
       </c>
       <c r="Y123" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z123" t="s">
         <v>78</v>
@@ -21218,7 +21233,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="124" spans="1:29">
+    <row r="124" spans="1:29" hidden="1">
       <c r="A124">
         <v>123</v>
       </c>
@@ -21292,7 +21307,7 @@
         <v>76</v>
       </c>
       <c r="Y124" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z124" t="s">
         <v>78</v>
@@ -21307,7 +21322,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="125" spans="1:29">
+    <row r="125" spans="1:29" hidden="1">
       <c r="A125">
         <v>124</v>
       </c>
@@ -21396,7 +21411,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="126" spans="1:29">
+    <row r="126" spans="1:29" hidden="1">
       <c r="A126">
         <v>125</v>
       </c>
@@ -21479,13 +21494,13 @@
         <v>45762</v>
       </c>
       <c r="AB126" t="s">
-        <v>45</v>
+        <v>3013</v>
       </c>
       <c r="AC126" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="127" spans="1:29">
+    <row r="127" spans="1:29" hidden="1">
       <c r="A127">
         <v>126</v>
       </c>
@@ -21574,7 +21589,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="128" spans="1:29">
+    <row r="128" spans="1:29" hidden="1">
       <c r="A128">
         <v>127</v>
       </c>
@@ -21648,7 +21663,7 @@
         <v>76</v>
       </c>
       <c r="Y128" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z128" t="s">
         <v>78</v>
@@ -21663,7 +21678,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="129" spans="1:29">
+    <row r="129" spans="1:29" hidden="1">
       <c r="A129">
         <v>128</v>
       </c>
@@ -21752,7 +21767,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="130" spans="1:29">
+    <row r="130" spans="1:29" hidden="1">
       <c r="A130">
         <v>129</v>
       </c>
@@ -21841,7 +21856,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="131" spans="1:29">
+    <row r="131" spans="1:29" hidden="1">
       <c r="A131">
         <v>130</v>
       </c>
@@ -21930,7 +21945,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="132" spans="1:29">
+    <row r="132" spans="1:29" hidden="1">
       <c r="A132">
         <v>131</v>
       </c>
@@ -22004,7 +22019,7 @@
         <v>76</v>
       </c>
       <c r="Y132" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z132" t="s">
         <v>78</v>
@@ -22019,7 +22034,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="133" spans="1:29">
+    <row r="133" spans="1:29" hidden="1">
       <c r="A133">
         <v>132</v>
       </c>
@@ -22108,7 +22123,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="134" spans="1:29">
+    <row r="134" spans="1:29" hidden="1">
       <c r="A134">
         <v>133</v>
       </c>
@@ -22197,7 +22212,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:29">
+    <row r="135" spans="1:29" hidden="1">
       <c r="A135">
         <v>134</v>
       </c>
@@ -22271,7 +22286,7 @@
         <v>76</v>
       </c>
       <c r="Y135" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z135" t="s">
         <v>78</v>
@@ -22286,7 +22301,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="136" spans="1:29">
+    <row r="136" spans="1:29" hidden="1">
       <c r="A136">
         <v>135</v>
       </c>
@@ -22360,7 +22375,7 @@
         <v>76</v>
       </c>
       <c r="Y136" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z136" t="s">
         <v>78</v>
@@ -22375,7 +22390,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:29">
+    <row r="137" spans="1:29" hidden="1">
       <c r="A137">
         <v>136</v>
       </c>
@@ -22464,7 +22479,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="138" spans="1:29">
+    <row r="138" spans="1:29" hidden="1">
       <c r="A138">
         <v>137</v>
       </c>
@@ -22553,7 +22568,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="139" spans="1:29">
+    <row r="139" spans="1:29" hidden="1">
       <c r="A139">
         <v>138</v>
       </c>
@@ -22642,7 +22657,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="140" spans="1:29">
+    <row r="140" spans="1:29" hidden="1">
       <c r="A140">
         <v>139</v>
       </c>
@@ -22716,7 +22731,7 @@
         <v>76</v>
       </c>
       <c r="Y140" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z140" t="s">
         <v>78</v>
@@ -22731,7 +22746,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="141" spans="1:29">
+    <row r="141" spans="1:29" hidden="1">
       <c r="A141">
         <v>140</v>
       </c>
@@ -22820,7 +22835,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="142" spans="1:29">
+    <row r="142" spans="1:29" hidden="1">
       <c r="A142">
         <v>141</v>
       </c>
@@ -22909,7 +22924,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="143" spans="1:29">
+    <row r="143" spans="1:29" hidden="1">
       <c r="A143">
         <v>142</v>
       </c>
@@ -22998,7 +23013,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="144" spans="1:29">
+    <row r="144" spans="1:29" hidden="1">
       <c r="A144">
         <v>143</v>
       </c>
@@ -23072,7 +23087,7 @@
         <v>76</v>
       </c>
       <c r="Y144" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z144" t="s">
         <v>78</v>
@@ -23087,7 +23102,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="145" spans="1:29">
+    <row r="145" spans="1:29" hidden="1">
       <c r="A145">
         <v>144</v>
       </c>
@@ -23176,7 +23191,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="146" spans="1:29">
+    <row r="146" spans="1:29" hidden="1">
       <c r="A146">
         <v>145</v>
       </c>
@@ -23265,7 +23280,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="147" spans="1:29">
+    <row r="147" spans="1:29" hidden="1">
       <c r="A147">
         <v>146</v>
       </c>
@@ -23354,7 +23369,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="148" spans="1:29">
+    <row r="148" spans="1:29" hidden="1">
       <c r="A148">
         <v>147</v>
       </c>
@@ -23428,7 +23443,7 @@
         <v>76</v>
       </c>
       <c r="Y148" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z148" t="s">
         <v>78</v>
@@ -23443,7 +23458,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="149" spans="1:29">
+    <row r="149" spans="1:29" hidden="1">
       <c r="A149">
         <v>148</v>
       </c>
@@ -23532,7 +23547,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="150" spans="1:29">
+    <row r="150" spans="1:29" hidden="1">
       <c r="A150">
         <v>149</v>
       </c>
@@ -23621,7 +23636,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="151" spans="1:29">
+    <row r="151" spans="1:29" hidden="1">
       <c r="A151">
         <v>150</v>
       </c>
@@ -23695,7 +23710,7 @@
         <v>76</v>
       </c>
       <c r="Y151" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z151" t="s">
         <v>78</v>
@@ -23710,7 +23725,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="152" spans="1:29">
+    <row r="152" spans="1:29" hidden="1">
       <c r="A152">
         <v>151</v>
       </c>
@@ -23784,7 +23799,7 @@
         <v>76</v>
       </c>
       <c r="Y152" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z152" t="s">
         <v>78</v>
@@ -23799,7 +23814,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="153" spans="1:29">
+    <row r="153" spans="1:29" hidden="1">
       <c r="A153">
         <v>152</v>
       </c>
@@ -23888,7 +23903,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="154" spans="1:29">
+    <row r="154" spans="1:29" hidden="1">
       <c r="A154">
         <v>153</v>
       </c>
@@ -23977,7 +23992,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="155" spans="1:29">
+    <row r="155" spans="1:29" hidden="1">
       <c r="A155">
         <v>154</v>
       </c>
@@ -24066,7 +24081,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="156" spans="1:29">
+    <row r="156" spans="1:29" hidden="1">
       <c r="A156">
         <v>155</v>
       </c>
@@ -24140,7 +24155,7 @@
         <v>76</v>
       </c>
       <c r="Y156" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z156" t="s">
         <v>78</v>
@@ -24155,7 +24170,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="157" spans="1:29">
+    <row r="157" spans="1:29" hidden="1">
       <c r="A157">
         <v>156</v>
       </c>
@@ -24238,13 +24253,13 @@
         <v>45790</v>
       </c>
       <c r="AB157" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC157" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="158" spans="1:29">
+    <row r="158" spans="1:29" hidden="1">
       <c r="A158">
         <v>157</v>
       </c>
@@ -24333,7 +24348,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="159" spans="1:29">
+    <row r="159" spans="1:29" hidden="1">
       <c r="A159">
         <v>158</v>
       </c>
@@ -24422,7 +24437,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="160" spans="1:29">
+    <row r="160" spans="1:29" hidden="1">
       <c r="A160">
         <v>159</v>
       </c>
@@ -24496,7 +24511,7 @@
         <v>76</v>
       </c>
       <c r="Y160" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z160" t="s">
         <v>78</v>
@@ -24511,7 +24526,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="161" spans="1:29">
+    <row r="161" spans="1:29" hidden="1">
       <c r="A161">
         <v>160</v>
       </c>
@@ -24600,7 +24615,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="162" spans="1:29">
+    <row r="162" spans="1:29" hidden="1">
       <c r="A162">
         <v>161</v>
       </c>
@@ -24689,7 +24704,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="163" spans="1:29">
+    <row r="163" spans="1:29" hidden="1">
       <c r="A163">
         <v>162</v>
       </c>
@@ -24763,7 +24778,7 @@
         <v>76</v>
       </c>
       <c r="Y163" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z163" t="s">
         <v>78</v>
@@ -24778,7 +24793,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="164" spans="1:29">
+    <row r="164" spans="1:29" hidden="1">
       <c r="A164">
         <v>163</v>
       </c>
@@ -24852,7 +24867,7 @@
         <v>76</v>
       </c>
       <c r="Y164" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z164" t="s">
         <v>78</v>
@@ -24867,7 +24882,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="165" spans="1:29">
+    <row r="165" spans="1:29" hidden="1">
       <c r="A165">
         <v>164</v>
       </c>
@@ -24956,7 +24971,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="166" spans="1:29">
+    <row r="166" spans="1:29" hidden="1">
       <c r="A166">
         <v>165</v>
       </c>
@@ -25045,7 +25060,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="167" spans="1:29">
+    <row r="167" spans="1:29" hidden="1">
       <c r="A167">
         <v>166</v>
       </c>
@@ -25134,7 +25149,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="168" spans="1:29">
+    <row r="168" spans="1:29" hidden="1">
       <c r="A168">
         <v>167</v>
       </c>
@@ -25208,7 +25223,7 @@
         <v>76</v>
       </c>
       <c r="Y168" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z168" t="s">
         <v>78</v>
@@ -25223,7 +25238,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="169" spans="1:29">
+    <row r="169" spans="1:29" hidden="1">
       <c r="A169">
         <v>168</v>
       </c>
@@ -25312,7 +25327,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="170" spans="1:29">
+    <row r="170" spans="1:29" hidden="1">
       <c r="A170">
         <v>169</v>
       </c>
@@ -25401,7 +25416,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="171" spans="1:29">
+    <row r="171" spans="1:29" hidden="1">
       <c r="A171">
         <v>170</v>
       </c>
@@ -25490,7 +25505,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="172" spans="1:29">
+    <row r="172" spans="1:29" hidden="1">
       <c r="A172">
         <v>171</v>
       </c>
@@ -25564,7 +25579,7 @@
         <v>76</v>
       </c>
       <c r="Y172" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z172" t="s">
         <v>78</v>
@@ -25579,7 +25594,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="173" spans="1:29">
+    <row r="173" spans="1:29" hidden="1">
       <c r="A173">
         <v>172</v>
       </c>
@@ -25668,7 +25683,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="174" spans="1:29">
+    <row r="174" spans="1:29" hidden="1">
       <c r="A174">
         <v>173</v>
       </c>
@@ -25757,7 +25772,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="175" spans="1:29">
+    <row r="175" spans="1:29" hidden="1">
       <c r="A175">
         <v>174</v>
       </c>
@@ -25831,7 +25846,7 @@
         <v>76</v>
       </c>
       <c r="Y175" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z175" t="s">
         <v>78</v>
@@ -25846,7 +25861,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="176" spans="1:29">
+    <row r="176" spans="1:29" hidden="1">
       <c r="A176">
         <v>175</v>
       </c>
@@ -25920,7 +25935,7 @@
         <v>76</v>
       </c>
       <c r="Y176" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z176" t="s">
         <v>78</v>
@@ -25935,7 +25950,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="177" spans="1:29">
+    <row r="177" spans="1:29" hidden="1">
       <c r="A177">
         <v>176</v>
       </c>
@@ -26024,7 +26039,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="178" spans="1:29">
+    <row r="178" spans="1:29" hidden="1">
       <c r="A178">
         <v>177</v>
       </c>
@@ -26113,7 +26128,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="179" spans="1:29">
+    <row r="179" spans="1:29" hidden="1">
       <c r="A179">
         <v>178</v>
       </c>
@@ -26202,7 +26217,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="180" spans="1:29">
+    <row r="180" spans="1:29" hidden="1">
       <c r="A180">
         <v>179</v>
       </c>
@@ -26276,7 +26291,7 @@
         <v>76</v>
       </c>
       <c r="Y180" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z180" t="s">
         <v>78</v>
@@ -26291,7 +26306,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="181" spans="1:29">
+    <row r="181" spans="1:29" hidden="1">
       <c r="A181">
         <v>180</v>
       </c>
@@ -26380,7 +26395,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="182" spans="1:29">
+    <row r="182" spans="1:29" hidden="1">
       <c r="A182">
         <v>181</v>
       </c>
@@ -26469,7 +26484,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="183" spans="1:29">
+    <row r="183" spans="1:29" hidden="1">
       <c r="A183">
         <v>182</v>
       </c>
@@ -26558,7 +26573,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="184" spans="1:29">
+    <row r="184" spans="1:29" hidden="1">
       <c r="A184">
         <v>183</v>
       </c>
@@ -26632,7 +26647,7 @@
         <v>76</v>
       </c>
       <c r="Y184" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z184" t="s">
         <v>78</v>
@@ -26647,7 +26662,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="185" spans="1:29">
+    <row r="185" spans="1:29" hidden="1">
       <c r="A185">
         <v>184</v>
       </c>
@@ -26736,7 +26751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="186" spans="1:29">
+    <row r="186" spans="1:29" hidden="1">
       <c r="A186">
         <v>185</v>
       </c>
@@ -26819,13 +26834,13 @@
         <v>45813</v>
       </c>
       <c r="AB186" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC186" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="187" spans="1:29">
+    <row r="187" spans="1:29" hidden="1">
       <c r="A187">
         <v>186</v>
       </c>
@@ -26899,7 +26914,7 @@
         <v>76</v>
       </c>
       <c r="Y187" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z187" t="s">
         <v>78</v>
@@ -26914,7 +26929,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="188" spans="1:29">
+    <row r="188" spans="1:29" hidden="1">
       <c r="A188">
         <v>187</v>
       </c>
@@ -26988,7 +27003,7 @@
         <v>76</v>
       </c>
       <c r="Y188" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z188" t="s">
         <v>78</v>
@@ -27003,7 +27018,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="189" spans="1:29">
+    <row r="189" spans="1:29" hidden="1">
       <c r="A189">
         <v>188</v>
       </c>
@@ -27092,7 +27107,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="190" spans="1:29">
+    <row r="190" spans="1:29" hidden="1">
       <c r="A190">
         <v>189</v>
       </c>
@@ -27175,13 +27190,13 @@
         <v>45816</v>
       </c>
       <c r="AB190" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC190" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="191" spans="1:29">
+    <row r="191" spans="1:29" hidden="1">
       <c r="A191">
         <v>190</v>
       </c>
@@ -27270,7 +27285,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="192" spans="1:29">
+    <row r="192" spans="1:29" hidden="1">
       <c r="A192">
         <v>191</v>
       </c>
@@ -27344,7 +27359,7 @@
         <v>76</v>
       </c>
       <c r="Y192" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z192" t="s">
         <v>78</v>
@@ -27359,7 +27374,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="193" spans="1:29">
+    <row r="193" spans="1:29" hidden="1">
       <c r="A193">
         <v>192</v>
       </c>
@@ -27448,7 +27463,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="194" spans="1:29">
+    <row r="194" spans="1:29" hidden="1">
       <c r="A194">
         <v>193</v>
       </c>
@@ -27537,7 +27552,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="195" spans="1:29">
+    <row r="195" spans="1:29" hidden="1">
       <c r="A195">
         <v>194</v>
       </c>
@@ -27626,7 +27641,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="196" spans="1:29">
+    <row r="196" spans="1:29" hidden="1">
       <c r="A196">
         <v>195</v>
       </c>
@@ -27700,7 +27715,7 @@
         <v>76</v>
       </c>
       <c r="Y196" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z196" t="s">
         <v>78</v>
@@ -27715,7 +27730,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="197" spans="1:29">
+    <row r="197" spans="1:29" hidden="1">
       <c r="A197">
         <v>196</v>
       </c>
@@ -27804,7 +27819,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="198" spans="1:29">
+    <row r="198" spans="1:29" hidden="1">
       <c r="A198">
         <v>197</v>
       </c>
@@ -27893,7 +27908,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="199" spans="1:29">
+    <row r="199" spans="1:29" hidden="1">
       <c r="A199">
         <v>198</v>
       </c>
@@ -27967,7 +27982,7 @@
         <v>76</v>
       </c>
       <c r="Y199" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z199" t="s">
         <v>78</v>
@@ -27982,7 +27997,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="200" spans="1:29">
+    <row r="200" spans="1:29" hidden="1">
       <c r="A200">
         <v>199</v>
       </c>
@@ -28056,7 +28071,7 @@
         <v>76</v>
       </c>
       <c r="Y200" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z200" t="s">
         <v>78</v>
@@ -28071,7 +28086,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="201" spans="1:29">
+    <row r="201" spans="1:29" hidden="1">
       <c r="A201">
         <v>200</v>
       </c>
@@ -28160,7 +28175,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="202" spans="1:29">
+    <row r="202" spans="1:29" hidden="1">
       <c r="A202">
         <v>201</v>
       </c>
@@ -28243,13 +28258,13 @@
         <v>45826</v>
       </c>
       <c r="AB202" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC202" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="203" spans="1:29">
+    <row r="203" spans="1:29" hidden="1">
       <c r="A203">
         <v>202</v>
       </c>
@@ -28338,7 +28353,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="204" spans="1:29">
+    <row r="204" spans="1:29" hidden="1">
       <c r="A204">
         <v>203</v>
       </c>
@@ -28412,7 +28427,7 @@
         <v>76</v>
       </c>
       <c r="Y204" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z204" t="s">
         <v>78</v>
@@ -28427,7 +28442,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="205" spans="1:29">
+    <row r="205" spans="1:29" hidden="1">
       <c r="A205">
         <v>204</v>
       </c>
@@ -28510,13 +28525,13 @@
         <v>45830</v>
       </c>
       <c r="AB205" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC205" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="206" spans="1:29">
+    <row r="206" spans="1:29" hidden="1">
       <c r="A206">
         <v>205</v>
       </c>
@@ -28599,13 +28614,13 @@
         <v>45829</v>
       </c>
       <c r="AB206" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC206" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="207" spans="1:29">
+    <row r="207" spans="1:29" hidden="1">
       <c r="A207">
         <v>206</v>
       </c>
@@ -28694,7 +28709,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="208" spans="1:29">
+    <row r="208" spans="1:29" hidden="1">
       <c r="A208">
         <v>207</v>
       </c>
@@ -28768,7 +28783,7 @@
         <v>76</v>
       </c>
       <c r="Y208" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z208" t="s">
         <v>78</v>
@@ -28783,7 +28798,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="209" spans="1:29">
+    <row r="209" spans="1:29" hidden="1">
       <c r="A209">
         <v>208</v>
       </c>
@@ -28872,7 +28887,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="210" spans="1:29">
+    <row r="210" spans="1:29" hidden="1">
       <c r="A210">
         <v>209</v>
       </c>
@@ -28955,13 +28970,13 @@
         <v>45837</v>
       </c>
       <c r="AB210" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC210" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="211" spans="1:29">
+    <row r="211" spans="1:29" hidden="1">
       <c r="A211">
         <v>210</v>
       </c>
@@ -29035,7 +29050,7 @@
         <v>76</v>
       </c>
       <c r="Y211" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z211" t="s">
         <v>78</v>
@@ -29050,7 +29065,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="212" spans="1:29">
+    <row r="212" spans="1:29" hidden="1">
       <c r="A212">
         <v>211</v>
       </c>
@@ -29124,7 +29139,7 @@
         <v>76</v>
       </c>
       <c r="Y212" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z212" t="s">
         <v>78</v>
@@ -29139,7 +29154,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="213" spans="1:29">
+    <row r="213" spans="1:29" hidden="1">
       <c r="A213">
         <v>212</v>
       </c>
@@ -29228,7 +29243,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="214" spans="1:29">
+    <row r="214" spans="1:29" hidden="1">
       <c r="A214">
         <v>213</v>
       </c>
@@ -29311,13 +29326,13 @@
         <v>45840</v>
       </c>
       <c r="AB214" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC214" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="215" spans="1:29">
+    <row r="215" spans="1:29" hidden="1">
       <c r="A215">
         <v>214</v>
       </c>
@@ -29406,7 +29421,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="216" spans="1:29">
+    <row r="216" spans="1:29" hidden="1">
       <c r="A216">
         <v>215</v>
       </c>
@@ -29480,7 +29495,7 @@
         <v>76</v>
       </c>
       <c r="Y216" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z216" t="s">
         <v>78</v>
@@ -29495,7 +29510,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="217" spans="1:29">
+    <row r="217" spans="1:29" hidden="1">
       <c r="A217">
         <v>216</v>
       </c>
@@ -29578,13 +29593,13 @@
         <v>45840</v>
       </c>
       <c r="AB217" t="s">
-        <v>45</v>
+        <v>3012</v>
       </c>
       <c r="AC217" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="218" spans="1:29">
+    <row r="218" spans="1:29" hidden="1">
       <c r="A218">
         <v>217</v>
       </c>
@@ -29673,7 +29688,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="219" spans="1:29">
+    <row r="219" spans="1:29" hidden="1">
       <c r="A219">
         <v>218</v>
       </c>
@@ -29762,7 +29777,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="220" spans="1:29">
+    <row r="220" spans="1:29" hidden="1">
       <c r="A220">
         <v>219</v>
       </c>
@@ -29836,7 +29851,7 @@
         <v>76</v>
       </c>
       <c r="Y220" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z220" t="s">
         <v>78</v>
@@ -29851,7 +29866,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="221" spans="1:29">
+    <row r="221" spans="1:29" hidden="1">
       <c r="A221">
         <v>220</v>
       </c>
@@ -29940,7 +29955,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="222" spans="1:29">
+    <row r="222" spans="1:29" hidden="1">
       <c r="A222">
         <v>221</v>
       </c>
@@ -30029,7 +30044,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="223" spans="1:29">
+    <row r="223" spans="1:29" hidden="1">
       <c r="A223">
         <v>222</v>
       </c>
@@ -30118,7 +30133,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="224" spans="1:29">
+    <row r="224" spans="1:29" hidden="1">
       <c r="A224">
         <v>223</v>
       </c>
@@ -30192,7 +30207,7 @@
         <v>76</v>
       </c>
       <c r="Y224" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z224" t="s">
         <v>78</v>
@@ -30207,7 +30222,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="225" spans="1:29">
+    <row r="225" spans="1:29" hidden="1">
       <c r="A225">
         <v>224</v>
       </c>
@@ -30296,7 +30311,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="226" spans="1:29">
+    <row r="226" spans="1:29" hidden="1">
       <c r="A226">
         <v>225</v>
       </c>
@@ -30385,7 +30400,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="227" spans="1:29">
+    <row r="227" spans="1:29" hidden="1">
       <c r="A227">
         <v>226</v>
       </c>
@@ -30474,7 +30489,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="228" spans="1:29">
+    <row r="228" spans="1:29" hidden="1">
       <c r="A228">
         <v>227</v>
       </c>
@@ -30563,7 +30578,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="229" spans="1:29">
+    <row r="229" spans="1:29" hidden="1">
       <c r="A229">
         <v>228</v>
       </c>
@@ -30652,7 +30667,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="230" spans="1:29">
+    <row r="230" spans="1:29" hidden="1">
       <c r="A230">
         <v>229</v>
       </c>
@@ -30741,7 +30756,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="231" spans="1:29">
+    <row r="231" spans="1:29" hidden="1">
       <c r="A231">
         <v>230</v>
       </c>
@@ -30830,7 +30845,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="232" spans="1:29">
+    <row r="232" spans="1:29" hidden="1">
       <c r="A232">
         <v>231</v>
       </c>
@@ -30904,7 +30919,7 @@
         <v>76</v>
       </c>
       <c r="Y232" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z232" t="s">
         <v>78</v>
@@ -30919,7 +30934,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="233" spans="1:29">
+    <row r="233" spans="1:29" hidden="1">
       <c r="A233">
         <v>232</v>
       </c>
@@ -31008,7 +31023,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="234" spans="1:29">
+    <row r="234" spans="1:29" hidden="1">
       <c r="A234">
         <v>233</v>
       </c>
@@ -31097,7 +31112,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="235" spans="1:29">
+    <row r="235" spans="1:29" hidden="1">
       <c r="A235">
         <v>234</v>
       </c>
@@ -31186,7 +31201,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="236" spans="1:29">
+    <row r="236" spans="1:29" hidden="1">
       <c r="A236">
         <v>235</v>
       </c>
@@ -31260,7 +31275,7 @@
         <v>76</v>
       </c>
       <c r="Y236" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z236" t="s">
         <v>78</v>
@@ -31275,7 +31290,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="237" spans="1:29">
+    <row r="237" spans="1:29" hidden="1">
       <c r="A237">
         <v>236</v>
       </c>
@@ -31364,7 +31379,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="238" spans="1:29">
+    <row r="238" spans="1:29" hidden="1">
       <c r="A238">
         <v>237</v>
       </c>
@@ -31453,7 +31468,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="239" spans="1:29">
+    <row r="239" spans="1:29" hidden="1">
       <c r="A239">
         <v>238</v>
       </c>
@@ -31542,7 +31557,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="240" spans="1:29">
+    <row r="240" spans="1:29" hidden="1">
       <c r="A240">
         <v>239</v>
       </c>
@@ -31631,7 +31646,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="241" spans="1:29">
+    <row r="241" spans="1:29" hidden="1">
       <c r="A241">
         <v>240</v>
       </c>
@@ -31720,7 +31735,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="242" spans="1:29">
+    <row r="242" spans="1:29" hidden="1">
       <c r="A242">
         <v>241</v>
       </c>
@@ -31809,7 +31824,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="243" spans="1:29">
+    <row r="243" spans="1:29" hidden="1">
       <c r="A243">
         <v>242</v>
       </c>
@@ -31898,7 +31913,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="244" spans="1:29">
+    <row r="244" spans="1:29" hidden="1">
       <c r="A244">
         <v>243</v>
       </c>
@@ -31972,7 +31987,7 @@
         <v>76</v>
       </c>
       <c r="Y244" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z244" t="s">
         <v>78</v>
@@ -31987,7 +32002,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="245" spans="1:29">
+    <row r="245" spans="1:29" hidden="1">
       <c r="A245">
         <v>244</v>
       </c>
@@ -32076,7 +32091,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="246" spans="1:29">
+    <row r="246" spans="1:29" hidden="1">
       <c r="A246">
         <v>245</v>
       </c>
@@ -32165,7 +32180,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="247" spans="1:29">
+    <row r="247" spans="1:29" hidden="1">
       <c r="A247">
         <v>246</v>
       </c>
@@ -32254,7 +32269,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="248" spans="1:29">
+    <row r="248" spans="1:29" hidden="1">
       <c r="A248">
         <v>247</v>
       </c>
@@ -32328,7 +32343,7 @@
         <v>76</v>
       </c>
       <c r="Y248" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z248" t="s">
         <v>78</v>
@@ -32343,7 +32358,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="249" spans="1:29">
+    <row r="249" spans="1:29" hidden="1">
       <c r="A249">
         <v>248</v>
       </c>
@@ -32432,7 +32447,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="250" spans="1:29">
+    <row r="250" spans="1:29" hidden="1">
       <c r="A250">
         <v>249</v>
       </c>
@@ -32521,7 +32536,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="251" spans="1:29">
+    <row r="251" spans="1:29" hidden="1">
       <c r="A251">
         <v>250</v>
       </c>
@@ -32610,7 +32625,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="252" spans="1:29">
+    <row r="252" spans="1:29" hidden="1">
       <c r="A252">
         <v>251</v>
       </c>
@@ -32699,7 +32714,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="253" spans="1:29">
+    <row r="253" spans="1:29" hidden="1">
       <c r="A253">
         <v>252</v>
       </c>
@@ -32788,7 +32803,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="254" spans="1:29">
+    <row r="254" spans="1:29" hidden="1">
       <c r="A254">
         <v>253</v>
       </c>
@@ -32877,7 +32892,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="255" spans="1:29">
+    <row r="255" spans="1:29" hidden="1">
       <c r="A255">
         <v>254</v>
       </c>
@@ -32966,7 +32981,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="256" spans="1:29">
+    <row r="256" spans="1:29" hidden="1">
       <c r="A256">
         <v>255</v>
       </c>
@@ -33040,7 +33055,7 @@
         <v>76</v>
       </c>
       <c r="Y256" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z256" t="s">
         <v>78</v>
@@ -33055,7 +33070,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="257" spans="1:29">
+    <row r="257" spans="1:29" hidden="1">
       <c r="A257">
         <v>256</v>
       </c>
@@ -33144,7 +33159,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="258" spans="1:29">
+    <row r="258" spans="1:29" hidden="1">
       <c r="A258">
         <v>257</v>
       </c>
@@ -33233,7 +33248,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="259" spans="1:29">
+    <row r="259" spans="1:29" hidden="1">
       <c r="A259">
         <v>258</v>
       </c>
@@ -33322,7 +33337,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="260" spans="1:29">
+    <row r="260" spans="1:29" hidden="1">
       <c r="A260">
         <v>259</v>
       </c>
@@ -33396,7 +33411,7 @@
         <v>76</v>
       </c>
       <c r="Y260" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z260" t="s">
         <v>78</v>
@@ -33411,7 +33426,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="261" spans="1:29">
+    <row r="261" spans="1:29" hidden="1">
       <c r="A261">
         <v>260</v>
       </c>
@@ -33500,7 +33515,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="262" spans="1:29">
+    <row r="262" spans="1:29" hidden="1">
       <c r="A262">
         <v>261</v>
       </c>
@@ -33589,7 +33604,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="263" spans="1:29">
+    <row r="263" spans="1:29" hidden="1">
       <c r="A263">
         <v>262</v>
       </c>
@@ -33678,7 +33693,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="264" spans="1:29">
+    <row r="264" spans="1:29" hidden="1">
       <c r="A264">
         <v>263</v>
       </c>
@@ -33767,7 +33782,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="265" spans="1:29">
+    <row r="265" spans="1:29" hidden="1">
       <c r="A265">
         <v>264</v>
       </c>
@@ -33856,7 +33871,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="266" spans="1:29">
+    <row r="266" spans="1:29" hidden="1">
       <c r="A266">
         <v>265</v>
       </c>
@@ -33945,7 +33960,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="267" spans="1:29">
+    <row r="267" spans="1:29" hidden="1">
       <c r="A267">
         <v>266</v>
       </c>
@@ -34034,7 +34049,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="268" spans="1:29">
+    <row r="268" spans="1:29" hidden="1">
       <c r="A268">
         <v>267</v>
       </c>
@@ -34108,7 +34123,7 @@
         <v>76</v>
       </c>
       <c r="Y268" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z268" t="s">
         <v>78</v>
@@ -34123,7 +34138,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="269" spans="1:29">
+    <row r="269" spans="1:29" hidden="1">
       <c r="A269">
         <v>268</v>
       </c>
@@ -34212,7 +34227,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="270" spans="1:29">
+    <row r="270" spans="1:29" hidden="1">
       <c r="A270">
         <v>269</v>
       </c>
@@ -34301,7 +34316,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="271" spans="1:29">
+    <row r="271" spans="1:29" hidden="1">
       <c r="A271">
         <v>270</v>
       </c>
@@ -34390,7 +34405,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="272" spans="1:29">
+    <row r="272" spans="1:29" hidden="1">
       <c r="A272">
         <v>271</v>
       </c>
@@ -34464,7 +34479,7 @@
         <v>76</v>
       </c>
       <c r="Y272" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z272" t="s">
         <v>78</v>
@@ -34479,7 +34494,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="273" spans="1:29">
+    <row r="273" spans="1:29" hidden="1">
       <c r="A273">
         <v>272</v>
       </c>
@@ -34568,7 +34583,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="274" spans="1:29">
+    <row r="274" spans="1:29" hidden="1">
       <c r="A274">
         <v>273</v>
       </c>
@@ -34657,7 +34672,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="275" spans="1:29">
+    <row r="275" spans="1:29" hidden="1">
       <c r="A275">
         <v>274</v>
       </c>
@@ -34746,7 +34761,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="276" spans="1:29">
+    <row r="276" spans="1:29" hidden="1">
       <c r="A276">
         <v>275</v>
       </c>
@@ -34835,7 +34850,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="277" spans="1:29">
+    <row r="277" spans="1:29" hidden="1">
       <c r="A277">
         <v>276</v>
       </c>
@@ -34924,7 +34939,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="278" spans="1:29">
+    <row r="278" spans="1:29" hidden="1">
       <c r="A278">
         <v>277</v>
       </c>
@@ -35013,7 +35028,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="279" spans="1:29">
+    <row r="279" spans="1:29" hidden="1">
       <c r="A279">
         <v>278</v>
       </c>
@@ -35102,7 +35117,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="280" spans="1:29">
+    <row r="280" spans="1:29" hidden="1">
       <c r="A280">
         <v>279</v>
       </c>
@@ -35176,7 +35191,7 @@
         <v>76</v>
       </c>
       <c r="Y280" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z280" t="s">
         <v>78</v>
@@ -35191,7 +35206,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="281" spans="1:29">
+    <row r="281" spans="1:29" hidden="1">
       <c r="A281">
         <v>280</v>
       </c>
@@ -35280,7 +35295,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="282" spans="1:29">
+    <row r="282" spans="1:29" hidden="1">
       <c r="A282">
         <v>281</v>
       </c>
@@ -35369,7 +35384,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="283" spans="1:29">
+    <row r="283" spans="1:29" hidden="1">
       <c r="A283">
         <v>282</v>
       </c>
@@ -35458,7 +35473,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="284" spans="1:29">
+    <row r="284" spans="1:29" hidden="1">
       <c r="A284">
         <v>283</v>
       </c>
@@ -35532,7 +35547,7 @@
         <v>76</v>
       </c>
       <c r="Y284" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z284" t="s">
         <v>78</v>
@@ -35547,7 +35562,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="285" spans="1:29">
+    <row r="285" spans="1:29" hidden="1">
       <c r="A285">
         <v>284</v>
       </c>
@@ -35636,7 +35651,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="286" spans="1:29">
+    <row r="286" spans="1:29" hidden="1">
       <c r="A286">
         <v>285</v>
       </c>
@@ -35725,7 +35740,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="287" spans="1:29">
+    <row r="287" spans="1:29" hidden="1">
       <c r="A287">
         <v>286</v>
       </c>
@@ -35814,7 +35829,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="288" spans="1:29">
+    <row r="288" spans="1:29" hidden="1">
       <c r="A288">
         <v>287</v>
       </c>
@@ -35903,7 +35918,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="289" spans="1:29">
+    <row r="289" spans="1:29" hidden="1">
       <c r="A289">
         <v>288</v>
       </c>
@@ -35992,7 +36007,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="290" spans="1:29">
+    <row r="290" spans="1:29" hidden="1">
       <c r="A290">
         <v>289</v>
       </c>
@@ -36081,7 +36096,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="291" spans="1:29">
+    <row r="291" spans="1:29" hidden="1">
       <c r="A291">
         <v>290</v>
       </c>
@@ -36170,7 +36185,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="292" spans="1:29">
+    <row r="292" spans="1:29" hidden="1">
       <c r="A292">
         <v>291</v>
       </c>
@@ -36244,7 +36259,7 @@
         <v>76</v>
       </c>
       <c r="Y292" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z292" t="s">
         <v>78</v>
@@ -36259,7 +36274,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="293" spans="1:29">
+    <row r="293" spans="1:29" hidden="1">
       <c r="A293">
         <v>292</v>
       </c>
@@ -36348,7 +36363,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="294" spans="1:29">
+    <row r="294" spans="1:29" hidden="1">
       <c r="A294">
         <v>293</v>
       </c>
@@ -36437,7 +36452,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="295" spans="1:29">
+    <row r="295" spans="1:29" hidden="1">
       <c r="A295">
         <v>294</v>
       </c>
@@ -36526,7 +36541,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="296" spans="1:29">
+    <row r="296" spans="1:29" hidden="1">
       <c r="A296">
         <v>295</v>
       </c>
@@ -36600,7 +36615,7 @@
         <v>76</v>
       </c>
       <c r="Y296" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z296" t="s">
         <v>78</v>
@@ -36615,7 +36630,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="297" spans="1:29">
+    <row r="297" spans="1:29" hidden="1">
       <c r="A297">
         <v>296</v>
       </c>
@@ -36704,7 +36719,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="298" spans="1:29">
+    <row r="298" spans="1:29" hidden="1">
       <c r="A298">
         <v>297</v>
       </c>
@@ -36793,7 +36808,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="299" spans="1:29">
+    <row r="299" spans="1:29" hidden="1">
       <c r="A299">
         <v>298</v>
       </c>
@@ -36882,7 +36897,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="300" spans="1:29">
+    <row r="300" spans="1:29" hidden="1">
       <c r="A300">
         <v>299</v>
       </c>
@@ -36971,7 +36986,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="301" spans="1:29">
+    <row r="301" spans="1:29" hidden="1">
       <c r="A301">
         <v>300</v>
       </c>
@@ -37060,7 +37075,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="302" spans="1:29">
+    <row r="302" spans="1:29" hidden="1">
       <c r="A302">
         <v>301</v>
       </c>
@@ -37149,7 +37164,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="303" spans="1:29">
+    <row r="303" spans="1:29" hidden="1">
       <c r="A303">
         <v>302</v>
       </c>
@@ -37238,7 +37253,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="304" spans="1:29">
+    <row r="304" spans="1:29" hidden="1">
       <c r="A304">
         <v>303</v>
       </c>
@@ -37312,7 +37327,7 @@
         <v>76</v>
       </c>
       <c r="Y304" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z304" t="s">
         <v>78</v>
@@ -37327,7 +37342,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="305" spans="1:29">
+    <row r="305" spans="1:29" hidden="1">
       <c r="A305">
         <v>304</v>
       </c>
@@ -37416,7 +37431,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="306" spans="1:29">
+    <row r="306" spans="1:29" hidden="1">
       <c r="A306">
         <v>305</v>
       </c>
@@ -37505,7 +37520,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="307" spans="1:29">
+    <row r="307" spans="1:29" hidden="1">
       <c r="A307">
         <v>306</v>
       </c>
@@ -37594,7 +37609,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="308" spans="1:29">
+    <row r="308" spans="1:29" hidden="1">
       <c r="A308">
         <v>307</v>
       </c>
@@ -37668,7 +37683,7 @@
         <v>76</v>
       </c>
       <c r="Y308" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z308" t="s">
         <v>78</v>
@@ -37683,7 +37698,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="309" spans="1:29">
+    <row r="309" spans="1:29" hidden="1">
       <c r="A309">
         <v>308</v>
       </c>
@@ -37772,7 +37787,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="310" spans="1:29">
+    <row r="310" spans="1:29" hidden="1">
       <c r="A310">
         <v>309</v>
       </c>
@@ -37861,7 +37876,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="311" spans="1:29">
+    <row r="311" spans="1:29" hidden="1">
       <c r="A311">
         <v>310</v>
       </c>
@@ -37950,7 +37965,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="312" spans="1:29">
+    <row r="312" spans="1:29" hidden="1">
       <c r="A312">
         <v>311</v>
       </c>
@@ -38039,7 +38054,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="313" spans="1:29">
+    <row r="313" spans="1:29" hidden="1">
       <c r="A313">
         <v>312</v>
       </c>
@@ -38128,7 +38143,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="314" spans="1:29">
+    <row r="314" spans="1:29" hidden="1">
       <c r="A314">
         <v>313</v>
       </c>
@@ -38217,7 +38232,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="315" spans="1:29">
+    <row r="315" spans="1:29" hidden="1">
       <c r="A315">
         <v>314</v>
       </c>
@@ -38306,7 +38321,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="316" spans="1:29">
+    <row r="316" spans="1:29" hidden="1">
       <c r="A316">
         <v>315</v>
       </c>
@@ -38380,7 +38395,7 @@
         <v>76</v>
       </c>
       <c r="Y316" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z316" t="s">
         <v>78</v>
@@ -38395,7 +38410,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="317" spans="1:29">
+    <row r="317" spans="1:29" hidden="1">
       <c r="A317">
         <v>316</v>
       </c>
@@ -38484,7 +38499,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="318" spans="1:29">
+    <row r="318" spans="1:29" hidden="1">
       <c r="A318">
         <v>317</v>
       </c>
@@ -38573,7 +38588,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="319" spans="1:29">
+    <row r="319" spans="1:29" hidden="1">
       <c r="A319">
         <v>318</v>
       </c>
@@ -38662,7 +38677,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="320" spans="1:29">
+    <row r="320" spans="1:29" hidden="1">
       <c r="A320">
         <v>319</v>
       </c>
@@ -38736,7 +38751,7 @@
         <v>76</v>
       </c>
       <c r="Y320" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z320" t="s">
         <v>78</v>
@@ -38751,7 +38766,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="321" spans="1:29">
+    <row r="321" spans="1:29" hidden="1">
       <c r="A321">
         <v>320</v>
       </c>
@@ -38840,7 +38855,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="322" spans="1:29">
+    <row r="322" spans="1:29" hidden="1">
       <c r="A322">
         <v>321</v>
       </c>
@@ -38929,7 +38944,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="323" spans="1:29">
+    <row r="323" spans="1:29" hidden="1">
       <c r="A323">
         <v>322</v>
       </c>
@@ -39018,7 +39033,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="324" spans="1:29">
+    <row r="324" spans="1:29" hidden="1">
       <c r="A324">
         <v>323</v>
       </c>
@@ -39107,7 +39122,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="325" spans="1:29">
+    <row r="325" spans="1:29" hidden="1">
       <c r="A325">
         <v>324</v>
       </c>
@@ -39196,7 +39211,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="326" spans="1:29">
+    <row r="326" spans="1:29" hidden="1">
       <c r="A326">
         <v>325</v>
       </c>
@@ -39285,7 +39300,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="327" spans="1:29">
+    <row r="327" spans="1:29" hidden="1">
       <c r="A327">
         <v>326</v>
       </c>
@@ -39374,7 +39389,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="328" spans="1:29">
+    <row r="328" spans="1:29" hidden="1">
       <c r="A328">
         <v>327</v>
       </c>
@@ -39448,7 +39463,7 @@
         <v>76</v>
       </c>
       <c r="Y328" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z328" t="s">
         <v>78</v>
@@ -39463,7 +39478,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="329" spans="1:29">
+    <row r="329" spans="1:29" hidden="1">
       <c r="A329">
         <v>328</v>
       </c>
@@ -39552,7 +39567,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="330" spans="1:29">
+    <row r="330" spans="1:29" hidden="1">
       <c r="A330">
         <v>329</v>
       </c>
@@ -39641,7 +39656,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="331" spans="1:29">
+    <row r="331" spans="1:29" hidden="1">
       <c r="A331">
         <v>330</v>
       </c>
@@ -39730,7 +39745,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="332" spans="1:29">
+    <row r="332" spans="1:29" hidden="1">
       <c r="A332">
         <v>331</v>
       </c>
@@ -39804,7 +39819,7 @@
         <v>76</v>
       </c>
       <c r="Y332" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z332" t="s">
         <v>78</v>
@@ -39819,7 +39834,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="333" spans="1:29">
+    <row r="333" spans="1:29" hidden="1">
       <c r="A333">
         <v>332</v>
       </c>
@@ -39908,7 +39923,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="334" spans="1:29">
+    <row r="334" spans="1:29" hidden="1">
       <c r="A334">
         <v>333</v>
       </c>
@@ -39997,7 +40012,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="335" spans="1:29">
+    <row r="335" spans="1:29" hidden="1">
       <c r="A335">
         <v>334</v>
       </c>
@@ -40086,7 +40101,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="336" spans="1:29">
+    <row r="336" spans="1:29" hidden="1">
       <c r="A336">
         <v>335</v>
       </c>
@@ -40160,7 +40175,7 @@
         <v>76</v>
       </c>
       <c r="Y336" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z336" t="s">
         <v>78</v>
@@ -40175,7 +40190,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="337" spans="1:29">
+    <row r="337" spans="1:29" hidden="1">
       <c r="A337">
         <v>336</v>
       </c>
@@ -40264,7 +40279,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="338" spans="1:29">
+    <row r="338" spans="1:29" hidden="1">
       <c r="A338">
         <v>337</v>
       </c>
@@ -40353,7 +40368,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="339" spans="1:29">
+    <row r="339" spans="1:29" hidden="1">
       <c r="A339">
         <v>338</v>
       </c>
@@ -40442,7 +40457,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="340" spans="1:29">
+    <row r="340" spans="1:29" hidden="1">
       <c r="A340">
         <v>339</v>
       </c>
@@ -40531,7 +40546,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="341" spans="1:29">
+    <row r="341" spans="1:29" hidden="1">
       <c r="A341">
         <v>340</v>
       </c>
@@ -40620,7 +40635,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="342" spans="1:29">
+    <row r="342" spans="1:29" hidden="1">
       <c r="A342">
         <v>341</v>
       </c>
@@ -40703,13 +40718,13 @@
         <v>45943</v>
       </c>
       <c r="AB342" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC342" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="343" spans="1:29">
+    <row r="343" spans="1:29" hidden="1">
       <c r="A343">
         <v>342</v>
       </c>
@@ -40798,7 +40813,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="344" spans="1:29">
+    <row r="344" spans="1:29" hidden="1">
       <c r="A344">
         <v>343</v>
       </c>
@@ -40872,7 +40887,7 @@
         <v>76</v>
       </c>
       <c r="Y344" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z344" t="s">
         <v>78</v>
@@ -40887,7 +40902,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="345" spans="1:29">
+    <row r="345" spans="1:29" hidden="1">
       <c r="A345">
         <v>344</v>
       </c>
@@ -40976,7 +40991,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="346" spans="1:29">
+    <row r="346" spans="1:29" hidden="1">
       <c r="A346">
         <v>345</v>
       </c>
@@ -41065,7 +41080,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="347" spans="1:29">
+    <row r="347" spans="1:29" hidden="1">
       <c r="A347">
         <v>346</v>
       </c>
@@ -41154,7 +41169,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="348" spans="1:29">
+    <row r="348" spans="1:29" hidden="1">
       <c r="A348">
         <v>347</v>
       </c>
@@ -41228,7 +41243,7 @@
         <v>76</v>
       </c>
       <c r="Y348" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z348" t="s">
         <v>78</v>
@@ -41243,7 +41258,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="349" spans="1:29">
+    <row r="349" spans="1:29" hidden="1">
       <c r="A349">
         <v>348</v>
       </c>
@@ -41332,7 +41347,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="350" spans="1:29">
+    <row r="350" spans="1:29" hidden="1">
       <c r="A350">
         <v>349</v>
       </c>
@@ -41415,13 +41430,13 @@
         <v>45954</v>
       </c>
       <c r="AB350" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC350" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="351" spans="1:29">
+    <row r="351" spans="1:29" hidden="1">
       <c r="A351">
         <v>350</v>
       </c>
@@ -41510,7 +41525,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="352" spans="1:29">
+    <row r="352" spans="1:29" hidden="1">
       <c r="A352">
         <v>351</v>
       </c>
@@ -41599,7 +41614,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="353" spans="1:29">
+    <row r="353" spans="1:29" hidden="1">
       <c r="A353">
         <v>352</v>
       </c>
@@ -41688,7 +41703,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="354" spans="1:29">
+    <row r="354" spans="1:29" hidden="1">
       <c r="A354">
         <v>353</v>
       </c>
@@ -41771,13 +41786,13 @@
         <v>45957</v>
       </c>
       <c r="AB354" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC354" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="355" spans="1:29">
+    <row r="355" spans="1:29" hidden="1">
       <c r="A355">
         <v>354</v>
       </c>
@@ -41866,7 +41881,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="356" spans="1:29">
+    <row r="356" spans="1:29" hidden="1">
       <c r="A356">
         <v>355</v>
       </c>
@@ -41940,7 +41955,7 @@
         <v>76</v>
       </c>
       <c r="Y356" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z356" t="s">
         <v>78</v>
@@ -41955,7 +41970,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="357" spans="1:29">
+    <row r="357" spans="1:29" hidden="1">
       <c r="A357">
         <v>356</v>
       </c>
@@ -42044,7 +42059,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="358" spans="1:29">
+    <row r="358" spans="1:29" hidden="1">
       <c r="A358">
         <v>357</v>
       </c>
@@ -42133,7 +42148,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="359" spans="1:29">
+    <row r="359" spans="1:29" hidden="1">
       <c r="A359">
         <v>358</v>
       </c>
@@ -42222,7 +42237,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="360" spans="1:29">
+    <row r="360" spans="1:29" hidden="1">
       <c r="A360">
         <v>359</v>
       </c>
@@ -42296,7 +42311,7 @@
         <v>76</v>
       </c>
       <c r="Y360" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z360" t="s">
         <v>78</v>
@@ -42311,7 +42326,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="361" spans="1:29">
+    <row r="361" spans="1:29" hidden="1">
       <c r="A361">
         <v>360</v>
       </c>
@@ -42400,7 +42415,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="362" spans="1:29">
+    <row r="362" spans="1:29" hidden="1">
       <c r="A362">
         <v>361</v>
       </c>
@@ -42483,13 +42498,13 @@
         <v>45960</v>
       </c>
       <c r="AB362" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC362" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="363" spans="1:29">
+    <row r="363" spans="1:29" hidden="1">
       <c r="A363">
         <v>362</v>
       </c>
@@ -42578,7 +42593,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="364" spans="1:29">
+    <row r="364" spans="1:29" hidden="1">
       <c r="A364">
         <v>363</v>
       </c>
@@ -42667,7 +42682,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="365" spans="1:29">
+    <row r="365" spans="1:29" hidden="1">
       <c r="A365">
         <v>364</v>
       </c>
@@ -42756,7 +42771,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="366" spans="1:29">
+    <row r="366" spans="1:29" hidden="1">
       <c r="A366">
         <v>365</v>
       </c>
@@ -42845,7 +42860,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="367" spans="1:29">
+    <row r="367" spans="1:29" hidden="1">
       <c r="A367">
         <v>366</v>
       </c>
@@ -42934,7 +42949,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="368" spans="1:29">
+    <row r="368" spans="1:29" hidden="1">
       <c r="A368">
         <v>367</v>
       </c>
@@ -43008,7 +43023,7 @@
         <v>76</v>
       </c>
       <c r="Y368" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z368" t="s">
         <v>78</v>
@@ -43023,7 +43038,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="369" spans="1:29">
+    <row r="369" spans="1:29" hidden="1">
       <c r="A369">
         <v>368</v>
       </c>
@@ -43112,7 +43127,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="370" spans="1:29">
+    <row r="370" spans="1:29" hidden="1">
       <c r="A370">
         <v>369</v>
       </c>
@@ -43201,7 +43216,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="371" spans="1:29">
+    <row r="371" spans="1:29" hidden="1">
       <c r="A371">
         <v>370</v>
       </c>
@@ -43290,7 +43305,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="372" spans="1:29">
+    <row r="372" spans="1:29" hidden="1">
       <c r="A372">
         <v>371</v>
       </c>
@@ -43364,7 +43379,7 @@
         <v>76</v>
       </c>
       <c r="Y372" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z372" t="s">
         <v>78</v>
@@ -43379,7 +43394,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="373" spans="1:29">
+    <row r="373" spans="1:29" hidden="1">
       <c r="A373">
         <v>372</v>
       </c>
@@ -43468,7 +43483,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="374" spans="1:29">
+    <row r="374" spans="1:29" hidden="1">
       <c r="A374">
         <v>373</v>
       </c>
@@ -43557,7 +43572,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="375" spans="1:29">
+    <row r="375" spans="1:29" hidden="1">
       <c r="A375">
         <v>374</v>
       </c>
@@ -43646,7 +43661,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="376" spans="1:29">
+    <row r="376" spans="1:29" hidden="1">
       <c r="A376">
         <v>375</v>
       </c>
@@ -43735,7 +43750,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="377" spans="1:29">
+    <row r="377" spans="1:29" hidden="1">
       <c r="A377">
         <v>376</v>
       </c>
@@ -43824,7 +43839,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="378" spans="1:29">
+    <row r="378" spans="1:29" hidden="1">
       <c r="A378">
         <v>377</v>
       </c>
@@ -43913,7 +43928,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="379" spans="1:29">
+    <row r="379" spans="1:29" hidden="1">
       <c r="A379">
         <v>378</v>
       </c>
@@ -44002,7 +44017,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="380" spans="1:29">
+    <row r="380" spans="1:29" hidden="1">
       <c r="A380">
         <v>379</v>
       </c>
@@ -44076,7 +44091,7 @@
         <v>76</v>
       </c>
       <c r="Y380" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z380" t="s">
         <v>78</v>
@@ -44091,7 +44106,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="381" spans="1:29">
+    <row r="381" spans="1:29" hidden="1">
       <c r="A381">
         <v>380</v>
       </c>
@@ -44180,7 +44195,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="382" spans="1:29">
+    <row r="382" spans="1:29" hidden="1">
       <c r="A382">
         <v>381</v>
       </c>
@@ -44269,7 +44284,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="383" spans="1:29">
+    <row r="383" spans="1:29" hidden="1">
       <c r="A383">
         <v>382</v>
       </c>
@@ -44358,7 +44373,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="384" spans="1:29">
+    <row r="384" spans="1:29" hidden="1">
       <c r="A384">
         <v>383</v>
       </c>
@@ -44432,7 +44447,7 @@
         <v>76</v>
       </c>
       <c r="Y384" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z384" t="s">
         <v>78</v>
@@ -44447,7 +44462,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="385" spans="1:29">
+    <row r="385" spans="1:29" hidden="1">
       <c r="A385">
         <v>384</v>
       </c>
@@ -44536,7 +44551,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="386" spans="1:29">
+    <row r="386" spans="1:29" hidden="1">
       <c r="A386">
         <v>385</v>
       </c>
@@ -44625,7 +44640,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="387" spans="1:29">
+    <row r="387" spans="1:29" hidden="1">
       <c r="A387">
         <v>386</v>
       </c>
@@ -44714,7 +44729,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="388" spans="1:29">
+    <row r="388" spans="1:29" hidden="1">
       <c r="A388">
         <v>387</v>
       </c>
@@ -44803,7 +44818,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="389" spans="1:29">
+    <row r="389" spans="1:29" hidden="1">
       <c r="A389">
         <v>388</v>
       </c>
@@ -44892,7 +44907,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="390" spans="1:29">
+    <row r="390" spans="1:29" hidden="1">
       <c r="A390">
         <v>389</v>
       </c>
@@ -44975,13 +44990,13 @@
         <v>45983</v>
       </c>
       <c r="AB390" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC390" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="391" spans="1:29">
+    <row r="391" spans="1:29" hidden="1">
       <c r="A391">
         <v>390</v>
       </c>
@@ -45070,7 +45085,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="392" spans="1:29">
+    <row r="392" spans="1:29" hidden="1">
       <c r="A392">
         <v>391</v>
       </c>
@@ -45144,7 +45159,7 @@
         <v>76</v>
       </c>
       <c r="Y392" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z392" t="s">
         <v>78</v>
@@ -45159,7 +45174,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="393" spans="1:29">
+    <row r="393" spans="1:29" hidden="1">
       <c r="A393">
         <v>392</v>
       </c>
@@ -45248,7 +45263,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="394" spans="1:29">
+    <row r="394" spans="1:29" hidden="1">
       <c r="A394">
         <v>393</v>
       </c>
@@ -45337,7 +45352,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="395" spans="1:29">
+    <row r="395" spans="1:29" hidden="1">
       <c r="A395">
         <v>394</v>
       </c>
@@ -45426,7 +45441,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="396" spans="1:29">
+    <row r="396" spans="1:29" hidden="1">
       <c r="A396">
         <v>395</v>
       </c>
@@ -45500,7 +45515,7 @@
         <v>76</v>
       </c>
       <c r="Y396" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z396" t="s">
         <v>78</v>
@@ -45515,7 +45530,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="397" spans="1:29">
+    <row r="397" spans="1:29" hidden="1">
       <c r="A397">
         <v>396</v>
       </c>
@@ -45604,7 +45619,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="398" spans="1:29">
+    <row r="398" spans="1:29" hidden="1">
       <c r="A398">
         <v>397</v>
       </c>
@@ -45687,13 +45702,13 @@
         <v>45994</v>
       </c>
       <c r="AB398" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC398" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="399" spans="1:29">
+    <row r="399" spans="1:29" hidden="1">
       <c r="A399">
         <v>398</v>
       </c>
@@ -45782,7 +45797,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="400" spans="1:29">
+    <row r="400" spans="1:29" hidden="1">
       <c r="A400">
         <v>399</v>
       </c>
@@ -45871,7 +45886,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="401" spans="1:29">
+    <row r="401" spans="1:29" hidden="1">
       <c r="A401">
         <v>400</v>
       </c>
@@ -45960,7 +45975,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="402" spans="1:29">
+    <row r="402" spans="1:29" hidden="1">
       <c r="A402">
         <v>401</v>
       </c>
@@ -46043,13 +46058,13 @@
         <v>45993</v>
       </c>
       <c r="AB402" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC402" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="403" spans="1:29">
+    <row r="403" spans="1:29" hidden="1">
       <c r="A403">
         <v>402</v>
       </c>
@@ -46138,7 +46153,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="404" spans="1:29">
+    <row r="404" spans="1:29" hidden="1">
       <c r="A404">
         <v>403</v>
       </c>
@@ -46212,7 +46227,7 @@
         <v>76</v>
       </c>
       <c r="Y404" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z404" t="s">
         <v>78</v>
@@ -46227,7 +46242,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="405" spans="1:29">
+    <row r="405" spans="1:29" hidden="1">
       <c r="A405">
         <v>404</v>
       </c>
@@ -46310,13 +46325,13 @@
         <v>45997</v>
       </c>
       <c r="AB405" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC405" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="406" spans="1:29">
+    <row r="406" spans="1:29" hidden="1">
       <c r="A406">
         <v>405</v>
       </c>
@@ -46405,7 +46420,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="407" spans="1:29">
+    <row r="407" spans="1:29" hidden="1">
       <c r="A407">
         <v>406</v>
       </c>
@@ -46494,7 +46509,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="408" spans="1:29">
+    <row r="408" spans="1:29" hidden="1">
       <c r="A408">
         <v>407</v>
       </c>
@@ -46568,7 +46583,7 @@
         <v>76</v>
       </c>
       <c r="Y408" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z408" t="s">
         <v>78</v>
@@ -46583,7 +46598,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="409" spans="1:29">
+    <row r="409" spans="1:29" hidden="1">
       <c r="A409">
         <v>408</v>
       </c>
@@ -46672,7 +46687,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="410" spans="1:29">
+    <row r="410" spans="1:29" hidden="1">
       <c r="A410">
         <v>409</v>
       </c>
@@ -46761,7 +46776,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="411" spans="1:29">
+    <row r="411" spans="1:29" hidden="1">
       <c r="A411">
         <v>410</v>
       </c>
@@ -46835,7 +46850,7 @@
         <v>76</v>
       </c>
       <c r="Y411" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z411" t="s">
         <v>78</v>
@@ -46850,7 +46865,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="412" spans="1:29">
+    <row r="412" spans="1:29" hidden="1">
       <c r="A412">
         <v>411</v>
       </c>
@@ -46924,7 +46939,7 @@
         <v>76</v>
       </c>
       <c r="Y412" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z412" t="s">
         <v>78</v>
@@ -46939,7 +46954,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="413" spans="1:29">
+    <row r="413" spans="1:29" hidden="1">
       <c r="A413">
         <v>412</v>
       </c>
@@ -47028,7 +47043,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="414" spans="1:29">
+    <row r="414" spans="1:29" hidden="1">
       <c r="A414">
         <v>413</v>
       </c>
@@ -47117,7 +47132,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="415" spans="1:29">
+    <row r="415" spans="1:29" hidden="1">
       <c r="A415">
         <v>414</v>
       </c>
@@ -47206,7 +47221,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="416" spans="1:29">
+    <row r="416" spans="1:29" hidden="1">
       <c r="A416">
         <v>415</v>
       </c>
@@ -47280,7 +47295,7 @@
         <v>76</v>
       </c>
       <c r="Y416" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z416" t="s">
         <v>78</v>
@@ -47295,7 +47310,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="417" spans="1:29">
+    <row r="417" spans="1:29" hidden="1">
       <c r="A417">
         <v>416</v>
       </c>
@@ -47384,7 +47399,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="418" spans="1:29">
+    <row r="418" spans="1:29" hidden="1">
       <c r="A418">
         <v>417</v>
       </c>
@@ -47473,7 +47488,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="419" spans="1:29">
+    <row r="419" spans="1:29" hidden="1">
       <c r="A419">
         <v>418</v>
       </c>
@@ -47562,7 +47577,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="420" spans="1:29">
+    <row r="420" spans="1:29" hidden="1">
       <c r="A420">
         <v>419</v>
       </c>
@@ -47636,7 +47651,7 @@
         <v>76</v>
       </c>
       <c r="Y420" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z420" t="s">
         <v>78</v>
@@ -47651,7 +47666,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="421" spans="1:29">
+    <row r="421" spans="1:29" hidden="1">
       <c r="A421">
         <v>420</v>
       </c>
@@ -47740,7 +47755,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="422" spans="1:29">
+    <row r="422" spans="1:29" hidden="1">
       <c r="A422">
         <v>421</v>
       </c>
@@ -47829,7 +47844,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="423" spans="1:29">
+    <row r="423" spans="1:29" hidden="1">
       <c r="A423">
         <v>422</v>
       </c>
@@ -47903,7 +47918,7 @@
         <v>76</v>
       </c>
       <c r="Y423" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z423" t="s">
         <v>78</v>
@@ -47918,7 +47933,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="424" spans="1:29">
+    <row r="424" spans="1:29" hidden="1">
       <c r="A424">
         <v>423</v>
       </c>
@@ -47992,7 +48007,7 @@
         <v>76</v>
       </c>
       <c r="Y424" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z424" t="s">
         <v>78</v>
@@ -48007,7 +48022,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="425" spans="1:29">
+    <row r="425" spans="1:29" hidden="1">
       <c r="A425">
         <v>424</v>
       </c>
@@ -48096,7 +48111,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="426" spans="1:29">
+    <row r="426" spans="1:29" hidden="1">
       <c r="A426">
         <v>425</v>
       </c>
@@ -48185,7 +48200,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="427" spans="1:29">
+    <row r="427" spans="1:29" hidden="1">
       <c r="A427">
         <v>426</v>
       </c>
@@ -48274,7 +48289,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="428" spans="1:29">
+    <row r="428" spans="1:29" hidden="1">
       <c r="A428">
         <v>427</v>
       </c>
@@ -48348,7 +48363,7 @@
         <v>76</v>
       </c>
       <c r="Y428" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z428" t="s">
         <v>78</v>
@@ -48363,7 +48378,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="429" spans="1:29">
+    <row r="429" spans="1:29" hidden="1">
       <c r="A429">
         <v>428</v>
       </c>
@@ -48452,7 +48467,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="430" spans="1:29">
+    <row r="430" spans="1:29" hidden="1">
       <c r="A430">
         <v>429</v>
       </c>
@@ -48541,7 +48556,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="431" spans="1:29">
+    <row r="431" spans="1:29" hidden="1">
       <c r="A431">
         <v>430</v>
       </c>
@@ -48630,7 +48645,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="432" spans="1:29">
+    <row r="432" spans="1:29" hidden="1">
       <c r="A432">
         <v>431</v>
       </c>
@@ -48704,7 +48719,7 @@
         <v>76</v>
       </c>
       <c r="Y432" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z432" t="s">
         <v>78</v>
@@ -48719,7 +48734,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="433" spans="1:29">
+    <row r="433" spans="1:29" hidden="1">
       <c r="A433">
         <v>432</v>
       </c>
@@ -48808,7 +48823,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="434" spans="1:29">
+    <row r="434" spans="1:29" hidden="1">
       <c r="A434">
         <v>433</v>
       </c>
@@ -48897,7 +48912,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="435" spans="1:29">
+    <row r="435" spans="1:29" hidden="1">
       <c r="A435">
         <v>434</v>
       </c>
@@ -48971,7 +48986,7 @@
         <v>76</v>
       </c>
       <c r="Y435" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z435" t="s">
         <v>78</v>
@@ -48986,7 +49001,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="436" spans="1:29">
+    <row r="436" spans="1:29" hidden="1">
       <c r="A436">
         <v>435</v>
       </c>
@@ -49060,7 +49075,7 @@
         <v>76</v>
       </c>
       <c r="Y436" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z436" t="s">
         <v>78</v>
@@ -49075,7 +49090,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="437" spans="1:29">
+    <row r="437" spans="1:29" hidden="1">
       <c r="A437">
         <v>436</v>
       </c>
@@ -49164,7 +49179,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="438" spans="1:29">
+    <row r="438" spans="1:29" hidden="1">
       <c r="A438">
         <v>437</v>
       </c>
@@ -49253,7 +49268,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="439" spans="1:29">
+    <row r="439" spans="1:29" hidden="1">
       <c r="A439">
         <v>438</v>
       </c>
@@ -49342,7 +49357,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="440" spans="1:29">
+    <row r="440" spans="1:29" hidden="1">
       <c r="A440">
         <v>439</v>
       </c>
@@ -49416,7 +49431,7 @@
         <v>76</v>
       </c>
       <c r="Y440" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z440" t="s">
         <v>78</v>
@@ -49431,7 +49446,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="441" spans="1:29">
+    <row r="441" spans="1:29" hidden="1">
       <c r="A441">
         <v>440</v>
       </c>
@@ -49609,7 +49624,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="443" spans="1:29">
+    <row r="443" spans="1:29" hidden="1">
       <c r="A443">
         <v>442</v>
       </c>
@@ -49683,7 +49698,7 @@
         <v>76</v>
       </c>
       <c r="Y443" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z443" t="s">
         <v>78</v>
@@ -49698,7 +49713,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="444" spans="1:29">
+    <row r="444" spans="1:29" hidden="1">
       <c r="A444">
         <v>443</v>
       </c>
@@ -49772,7 +49787,7 @@
         <v>76</v>
       </c>
       <c r="Y444" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z444" t="s">
         <v>78</v>
@@ -49787,7 +49802,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="445" spans="1:29">
+    <row r="445" spans="1:29" hidden="1">
       <c r="A445">
         <v>444</v>
       </c>
@@ -49959,13 +49974,13 @@
         <v>46034</v>
       </c>
       <c r="AB446" t="s">
-        <v>3011</v>
+        <v>45</v>
       </c>
       <c r="AC446" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="447" spans="1:29">
+    <row r="447" spans="1:29" hidden="1">
       <c r="A447">
         <v>446</v>
       </c>
@@ -50054,7 +50069,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="448" spans="1:29">
+    <row r="448" spans="1:29" hidden="1">
       <c r="A448">
         <v>447</v>
       </c>
@@ -50128,7 +50143,7 @@
         <v>76</v>
       </c>
       <c r="Y448" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z448" t="s">
         <v>78</v>
@@ -50315,13 +50330,13 @@
         <v>46033</v>
       </c>
       <c r="AB450" t="s">
-        <v>3013</v>
+        <v>45</v>
       </c>
       <c r="AC450" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="451" spans="1:29">
+    <row r="451" spans="1:29" hidden="1">
       <c r="A451">
         <v>450</v>
       </c>
@@ -50410,7 +50425,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="452" spans="1:29">
+    <row r="452" spans="1:29" hidden="1">
       <c r="A452">
         <v>451</v>
       </c>
@@ -50484,7 +50499,7 @@
         <v>76</v>
       </c>
       <c r="Y452" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z452" t="s">
         <v>78</v>
@@ -50499,7 +50514,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="453" spans="1:29">
+    <row r="453" spans="1:29" hidden="1">
       <c r="A453">
         <v>452</v>
       </c>
@@ -50677,7 +50692,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="455" spans="1:29">
+    <row r="455" spans="1:29" hidden="1">
       <c r="A455">
         <v>454</v>
       </c>
@@ -50751,7 +50766,7 @@
         <v>76</v>
       </c>
       <c r="Y455" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z455" t="s">
         <v>78</v>
@@ -50766,7 +50781,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="456" spans="1:29">
+    <row r="456" spans="1:29" hidden="1">
       <c r="A456">
         <v>455</v>
       </c>
@@ -50840,7 +50855,7 @@
         <v>76</v>
       </c>
       <c r="Y456" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z456" t="s">
         <v>78</v>
@@ -50855,7 +50870,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="457" spans="1:29">
+    <row r="457" spans="1:29" hidden="1">
       <c r="A457">
         <v>456</v>
       </c>
@@ -51027,13 +51042,13 @@
         <v>46044</v>
       </c>
       <c r="AB458" t="s">
-        <v>3011</v>
+        <v>45</v>
       </c>
       <c r="AC458" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="459" spans="1:29">
+    <row r="459" spans="1:29" hidden="1">
       <c r="A459">
         <v>458</v>
       </c>
@@ -51122,7 +51137,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="460" spans="1:29">
+    <row r="460" spans="1:29" hidden="1">
       <c r="A460">
         <v>459</v>
       </c>
@@ -51196,7 +51211,7 @@
         <v>76</v>
       </c>
       <c r="Y460" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z460" t="s">
         <v>78</v>
@@ -51294,7 +51309,7 @@
         <v>46044</v>
       </c>
       <c r="AB461" t="s">
-        <v>3011</v>
+        <v>45</v>
       </c>
       <c r="AC461" t="s">
         <v>46</v>
@@ -51389,7 +51404,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="463" spans="1:29">
+    <row r="463" spans="1:29" hidden="1">
       <c r="A463">
         <v>462</v>
       </c>
@@ -51478,7 +51493,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="464" spans="1:29">
+    <row r="464" spans="1:29" hidden="1">
       <c r="A464">
         <v>463</v>
       </c>
@@ -51552,7 +51567,7 @@
         <v>76</v>
       </c>
       <c r="Y464" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z464" t="s">
         <v>78</v>
@@ -51567,7 +51582,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="465" spans="1:29">
+    <row r="465" spans="1:29" hidden="1">
       <c r="A465">
         <v>464</v>
       </c>
@@ -51745,7 +51760,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="467" spans="1:29">
+    <row r="467" spans="1:29" hidden="1">
       <c r="A467">
         <v>466</v>
       </c>
@@ -51819,7 +51834,7 @@
         <v>76</v>
       </c>
       <c r="Y467" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z467" t="s">
         <v>78</v>
@@ -51834,7 +51849,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="468" spans="1:29">
+    <row r="468" spans="1:29" hidden="1">
       <c r="A468">
         <v>467</v>
       </c>
@@ -51908,7 +51923,7 @@
         <v>76</v>
       </c>
       <c r="Y468" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z468" t="s">
         <v>78</v>
@@ -51923,7 +51938,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="469" spans="1:29">
+    <row r="469" spans="1:29" hidden="1">
       <c r="A469">
         <v>468</v>
       </c>
@@ -52101,7 +52116,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="471" spans="1:29">
+    <row r="471" spans="1:29" hidden="1">
       <c r="A471">
         <v>470</v>
       </c>
@@ -52190,7 +52205,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="472" spans="1:29">
+    <row r="472" spans="1:29" hidden="1">
       <c r="A472">
         <v>471</v>
       </c>
@@ -52264,7 +52279,7 @@
         <v>76</v>
       </c>
       <c r="Y472" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z472" t="s">
         <v>78</v>
@@ -52457,7 +52472,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="475" spans="1:29">
+    <row r="475" spans="1:29" hidden="1">
       <c r="A475">
         <v>474</v>
       </c>
@@ -52546,7 +52561,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="476" spans="1:29">
+    <row r="476" spans="1:29" hidden="1">
       <c r="A476">
         <v>475</v>
       </c>
@@ -52620,7 +52635,7 @@
         <v>76</v>
       </c>
       <c r="Y476" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z476" t="s">
         <v>78</v>
@@ -52635,7 +52650,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="477" spans="1:29">
+    <row r="477" spans="1:29" hidden="1">
       <c r="A477">
         <v>476</v>
       </c>
@@ -52813,7 +52828,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="479" spans="1:29">
+    <row r="479" spans="1:29" hidden="1">
       <c r="A479">
         <v>478</v>
       </c>
@@ -52887,7 +52902,7 @@
         <v>76</v>
       </c>
       <c r="Y479" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z479" t="s">
         <v>78</v>
@@ -52902,7 +52917,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="480" spans="1:29">
+    <row r="480" spans="1:29" hidden="1">
       <c r="A480">
         <v>479</v>
       </c>
@@ -52976,7 +52991,7 @@
         <v>76</v>
       </c>
       <c r="Y480" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z480" t="s">
         <v>78</v>
@@ -52991,7 +53006,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="481" spans="1:29">
+    <row r="481" spans="1:29" hidden="1">
       <c r="A481">
         <v>480</v>
       </c>
@@ -53169,7 +53184,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="483" spans="1:29">
+    <row r="483" spans="1:29" hidden="1">
       <c r="A483">
         <v>482</v>
       </c>
@@ -53258,7 +53273,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="484" spans="1:29">
+    <row r="484" spans="1:29" hidden="1">
       <c r="A484">
         <v>483</v>
       </c>
@@ -53332,7 +53347,7 @@
         <v>76</v>
       </c>
       <c r="Y484" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z484" t="s">
         <v>78</v>
@@ -53519,13 +53534,13 @@
         <v>46067</v>
       </c>
       <c r="AB486" t="s">
-        <v>3012</v>
+        <v>45</v>
       </c>
       <c r="AC486" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="487" spans="1:29">
+    <row r="487" spans="1:29" hidden="1">
       <c r="A487">
         <v>486</v>
       </c>
@@ -53614,7 +53629,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="488" spans="1:29">
+    <row r="488" spans="1:29" hidden="1">
       <c r="A488">
         <v>487</v>
       </c>
@@ -53688,7 +53703,7 @@
         <v>76</v>
       </c>
       <c r="Y488" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z488" t="s">
         <v>78</v>
@@ -53703,7 +53718,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="489" spans="1:29">
+    <row r="489" spans="1:29" hidden="1">
       <c r="A489">
         <v>488</v>
       </c>
@@ -53881,7 +53896,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="491" spans="1:29">
+    <row r="491" spans="1:29" hidden="1">
       <c r="A491">
         <v>490</v>
       </c>
@@ -53955,7 +53970,7 @@
         <v>76</v>
       </c>
       <c r="Y491" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z491" t="s">
         <v>78</v>
@@ -53970,7 +53985,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="492" spans="1:29">
+    <row r="492" spans="1:29" hidden="1">
       <c r="A492">
         <v>491</v>
       </c>
@@ -54044,7 +54059,7 @@
         <v>76</v>
       </c>
       <c r="Y492" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z492" t="s">
         <v>78</v>
@@ -54059,7 +54074,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="493" spans="1:29">
+    <row r="493" spans="1:29" hidden="1">
       <c r="A493">
         <v>492</v>
       </c>
@@ -54237,7 +54252,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="495" spans="1:29">
+    <row r="495" spans="1:29" hidden="1">
       <c r="A495">
         <v>494</v>
       </c>
@@ -54326,7 +54341,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="496" spans="1:29">
+    <row r="496" spans="1:29" hidden="1">
       <c r="A496">
         <v>495</v>
       </c>
@@ -54400,7 +54415,7 @@
         <v>76</v>
       </c>
       <c r="Y496" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z496" t="s">
         <v>78</v>
@@ -54498,7 +54513,7 @@
         <v>46074</v>
       </c>
       <c r="AB497" t="s">
-        <v>3011</v>
+        <v>45</v>
       </c>
       <c r="AC497" t="s">
         <v>46</v>
@@ -54593,7 +54608,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="499" spans="1:29">
+    <row r="499" spans="1:29" hidden="1">
       <c r="A499">
         <v>498</v>
       </c>
@@ -54682,7 +54697,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="500" spans="1:29">
+    <row r="500" spans="1:29" hidden="1">
       <c r="A500">
         <v>499</v>
       </c>
@@ -54756,7 +54771,7 @@
         <v>76</v>
       </c>
       <c r="Y500" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z500" t="s">
         <v>78</v>
@@ -54771,7 +54786,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="501" spans="1:29">
+    <row r="501" spans="1:29" hidden="1">
       <c r="A501">
         <v>500</v>
       </c>
@@ -54949,7 +54964,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="503" spans="1:29">
+    <row r="503" spans="1:29" hidden="1">
       <c r="A503">
         <v>502</v>
       </c>
@@ -55023,7 +55038,7 @@
         <v>76</v>
       </c>
       <c r="Y503" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z503" t="s">
         <v>78</v>
@@ -55038,7 +55053,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="504" spans="1:29">
+    <row r="504" spans="1:29" hidden="1">
       <c r="A504">
         <v>503</v>
       </c>
@@ -55112,7 +55127,7 @@
         <v>76</v>
       </c>
       <c r="Y504" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z504" t="s">
         <v>78</v>
@@ -55127,7 +55142,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="505" spans="1:29">
+    <row r="505" spans="1:29" hidden="1">
       <c r="A505">
         <v>504</v>
       </c>
@@ -55305,7 +55320,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="507" spans="1:29">
+    <row r="507" spans="1:29" hidden="1">
       <c r="A507">
         <v>506</v>
       </c>
@@ -55394,7 +55409,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="508" spans="1:29">
+    <row r="508" spans="1:29" hidden="1">
       <c r="A508">
         <v>507</v>
       </c>
@@ -55468,7 +55483,7 @@
         <v>76</v>
       </c>
       <c r="Y508" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z508" t="s">
         <v>78</v>
@@ -55661,7 +55676,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="511" spans="1:29">
+    <row r="511" spans="1:29" hidden="1">
       <c r="A511">
         <v>510</v>
       </c>
@@ -55750,7 +55765,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="512" spans="1:29">
+    <row r="512" spans="1:29" hidden="1">
       <c r="A512">
         <v>511</v>
       </c>
@@ -55839,7 +55854,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="513" spans="1:29">
+    <row r="513" spans="1:29" hidden="1">
       <c r="A513">
         <v>512</v>
       </c>
@@ -56017,7 +56032,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="515" spans="1:29">
+    <row r="515" spans="1:29" hidden="1">
       <c r="A515">
         <v>514</v>
       </c>
@@ -56106,7 +56121,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="516" spans="1:29">
+    <row r="516" spans="1:29" hidden="1">
       <c r="A516">
         <v>515</v>
       </c>
@@ -56180,7 +56195,7 @@
         <v>76</v>
       </c>
       <c r="Y516" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z516" t="s">
         <v>78</v>
@@ -56195,7 +56210,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="517" spans="1:29">
+    <row r="517" spans="1:29" hidden="1">
       <c r="A517">
         <v>516</v>
       </c>
@@ -56284,7 +56299,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="518" spans="1:29">
+    <row r="518" spans="1:29" hidden="1">
       <c r="A518">
         <v>517</v>
       </c>
@@ -56373,7 +56388,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="519" spans="1:29">
+    <row r="519" spans="1:29" hidden="1">
       <c r="A519">
         <v>518</v>
       </c>
@@ -56462,7 +56477,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="520" spans="1:29">
+    <row r="520" spans="1:29" hidden="1">
       <c r="A520">
         <v>519</v>
       </c>
@@ -56536,7 +56551,7 @@
         <v>76</v>
       </c>
       <c r="Y520" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z520" t="s">
         <v>78</v>
@@ -56551,7 +56566,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="521" spans="1:29">
+    <row r="521" spans="1:29" hidden="1">
       <c r="A521">
         <v>520</v>
       </c>
@@ -56729,7 +56744,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="523" spans="1:29">
+    <row r="523" spans="1:29" hidden="1">
       <c r="A523">
         <v>522</v>
       </c>
@@ -56818,7 +56833,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="524" spans="1:29">
+    <row r="524" spans="1:29" hidden="1">
       <c r="A524">
         <v>523</v>
       </c>
@@ -56907,7 +56922,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="525" spans="1:29">
+    <row r="525" spans="1:29" hidden="1">
       <c r="A525">
         <v>524</v>
       </c>
@@ -57085,7 +57100,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="527" spans="1:29">
+    <row r="527" spans="1:29" hidden="1">
       <c r="A527">
         <v>526</v>
       </c>
@@ -57174,7 +57189,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="528" spans="1:29">
+    <row r="528" spans="1:29" hidden="1">
       <c r="A528">
         <v>527</v>
       </c>
@@ -57248,7 +57263,7 @@
         <v>76</v>
       </c>
       <c r="Y528" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z528" t="s">
         <v>78</v>
@@ -57263,7 +57278,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="529" spans="1:29">
+    <row r="529" spans="1:29" hidden="1">
       <c r="A529">
         <v>528</v>
       </c>
@@ -57352,7 +57367,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="530" spans="1:29">
+    <row r="530" spans="1:29" hidden="1">
       <c r="A530">
         <v>529</v>
       </c>
@@ -57441,7 +57456,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="531" spans="1:29">
+    <row r="531" spans="1:29" hidden="1">
       <c r="A531">
         <v>530</v>
       </c>
@@ -57530,7 +57545,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="532" spans="1:29">
+    <row r="532" spans="1:29" hidden="1">
       <c r="A532">
         <v>531</v>
       </c>
@@ -57604,7 +57619,7 @@
         <v>76</v>
       </c>
       <c r="Y532" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z532" t="s">
         <v>78</v>
@@ -57619,7 +57634,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="533" spans="1:29">
+    <row r="533" spans="1:29" hidden="1">
       <c r="A533">
         <v>532</v>
       </c>
@@ -57797,7 +57812,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="535" spans="1:29">
+    <row r="535" spans="1:29" hidden="1">
       <c r="A535">
         <v>534</v>
       </c>
@@ -57886,7 +57901,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="536" spans="1:29">
+    <row r="536" spans="1:29" hidden="1">
       <c r="A536">
         <v>535</v>
       </c>
@@ -57975,7 +57990,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="537" spans="1:29">
+    <row r="537" spans="1:29" hidden="1">
       <c r="A537">
         <v>536</v>
       </c>
@@ -58153,7 +58168,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="539" spans="1:29">
+    <row r="539" spans="1:29" hidden="1">
       <c r="A539">
         <v>538</v>
       </c>
@@ -58242,7 +58257,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="540" spans="1:29">
+    <row r="540" spans="1:29" hidden="1">
       <c r="A540">
         <v>539</v>
       </c>
@@ -58316,7 +58331,7 @@
         <v>76</v>
       </c>
       <c r="Y540" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z540" t="s">
         <v>78</v>
@@ -58331,7 +58346,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="541" spans="1:29">
+    <row r="541" spans="1:29" hidden="1">
       <c r="A541">
         <v>540</v>
       </c>
@@ -58420,7 +58435,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="542" spans="1:29">
+    <row r="542" spans="1:29" hidden="1">
       <c r="A542">
         <v>541</v>
       </c>
@@ -58509,7 +58524,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="543" spans="1:29">
+    <row r="543" spans="1:29" hidden="1">
       <c r="A543">
         <v>542</v>
       </c>
@@ -58598,7 +58613,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="544" spans="1:29">
+    <row r="544" spans="1:29" hidden="1">
       <c r="A544">
         <v>543</v>
       </c>
@@ -58672,7 +58687,7 @@
         <v>76</v>
       </c>
       <c r="Y544" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z544" t="s">
         <v>78</v>
@@ -58687,7 +58702,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="545" spans="1:29">
+    <row r="545" spans="1:29" hidden="1">
       <c r="A545">
         <v>544</v>
       </c>
@@ -58865,7 +58880,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="547" spans="1:29">
+    <row r="547" spans="1:29" hidden="1">
       <c r="A547">
         <v>546</v>
       </c>
@@ -58954,7 +58969,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="548" spans="1:29">
+    <row r="548" spans="1:29" hidden="1">
       <c r="A548">
         <v>547</v>
       </c>
@@ -59043,7 +59058,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="549" spans="1:29">
+    <row r="549" spans="1:29" hidden="1">
       <c r="A549">
         <v>548</v>
       </c>
@@ -59221,7 +59236,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="551" spans="1:29">
+    <row r="551" spans="1:29" hidden="1">
       <c r="A551">
         <v>550</v>
       </c>
@@ -59310,7 +59325,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="552" spans="1:29">
+    <row r="552" spans="1:29" hidden="1">
       <c r="A552">
         <v>551</v>
       </c>
@@ -59384,7 +59399,7 @@
         <v>76</v>
       </c>
       <c r="Y552" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z552" t="s">
         <v>78</v>
@@ -59399,7 +59414,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="553" spans="1:29">
+    <row r="553" spans="1:29" hidden="1">
       <c r="A553">
         <v>552</v>
       </c>
@@ -59488,7 +59503,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="554" spans="1:29">
+    <row r="554" spans="1:29" hidden="1">
       <c r="A554">
         <v>553</v>
       </c>
@@ -59577,7 +59592,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="555" spans="1:29">
+    <row r="555" spans="1:29" hidden="1">
       <c r="A555">
         <v>554</v>
       </c>
@@ -59666,7 +59681,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="556" spans="1:29">
+    <row r="556" spans="1:29" hidden="1">
       <c r="A556">
         <v>555</v>
       </c>
@@ -59740,7 +59755,7 @@
         <v>76</v>
       </c>
       <c r="Y556" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z556" t="s">
         <v>78</v>
@@ -59755,7 +59770,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="557" spans="1:29">
+    <row r="557" spans="1:29" hidden="1">
       <c r="A557">
         <v>556</v>
       </c>
@@ -59933,7 +59948,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="559" spans="1:29">
+    <row r="559" spans="1:29" hidden="1">
       <c r="A559">
         <v>558</v>
       </c>
@@ -60022,7 +60037,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="560" spans="1:29">
+    <row r="560" spans="1:29" hidden="1">
       <c r="A560">
         <v>559</v>
       </c>
@@ -60111,7 +60126,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="561" spans="1:29">
+    <row r="561" spans="1:29" hidden="1">
       <c r="A561">
         <v>560</v>
       </c>
@@ -60289,7 +60304,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="563" spans="1:29">
+    <row r="563" spans="1:29" hidden="1">
       <c r="A563">
         <v>562</v>
       </c>
@@ -60378,7 +60393,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="564" spans="1:29">
+    <row r="564" spans="1:29" hidden="1">
       <c r="A564">
         <v>563</v>
       </c>
@@ -60452,7 +60467,7 @@
         <v>76</v>
       </c>
       <c r="Y564" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z564" t="s">
         <v>78</v>
@@ -60467,7 +60482,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="565" spans="1:29">
+    <row r="565" spans="1:29" hidden="1">
       <c r="A565">
         <v>564</v>
       </c>
@@ -60556,7 +60571,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="566" spans="1:29">
+    <row r="566" spans="1:29" hidden="1">
       <c r="A566">
         <v>565</v>
       </c>
@@ -60645,7 +60660,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="567" spans="1:29">
+    <row r="567" spans="1:29" hidden="1">
       <c r="A567">
         <v>566</v>
       </c>
@@ -60734,7 +60749,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="568" spans="1:29">
+    <row r="568" spans="1:29" hidden="1">
       <c r="A568">
         <v>567</v>
       </c>
@@ -60808,7 +60823,7 @@
         <v>76</v>
       </c>
       <c r="Y568" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z568" t="s">
         <v>78</v>
@@ -60823,7 +60838,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="569" spans="1:29">
+    <row r="569" spans="1:29" hidden="1">
       <c r="A569">
         <v>568</v>
       </c>
@@ -61001,7 +61016,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="571" spans="1:29">
+    <row r="571" spans="1:29" hidden="1">
       <c r="A571">
         <v>570</v>
       </c>
@@ -61090,7 +61105,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="572" spans="1:29">
+    <row r="572" spans="1:29" hidden="1">
       <c r="A572">
         <v>571</v>
       </c>
@@ -61179,7 +61194,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="573" spans="1:29">
+    <row r="573" spans="1:29" hidden="1">
       <c r="A573">
         <v>572</v>
       </c>
@@ -61357,7 +61372,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="575" spans="1:29">
+    <row r="575" spans="1:29" hidden="1">
       <c r="A575">
         <v>574</v>
       </c>
@@ -61446,7 +61461,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="576" spans="1:29">
+    <row r="576" spans="1:29" hidden="1">
       <c r="A576">
         <v>575</v>
       </c>
@@ -61520,7 +61535,7 @@
         <v>76</v>
       </c>
       <c r="Y576" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z576" t="s">
         <v>78</v>
@@ -61535,7 +61550,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="577" spans="1:29">
+    <row r="577" spans="1:29" hidden="1">
       <c r="A577">
         <v>576</v>
       </c>
@@ -61624,7 +61639,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="578" spans="1:29">
+    <row r="578" spans="1:29" hidden="1">
       <c r="A578">
         <v>577</v>
       </c>
@@ -61713,7 +61728,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="579" spans="1:29">
+    <row r="579" spans="1:29" hidden="1">
       <c r="A579">
         <v>578</v>
       </c>
@@ -61802,7 +61817,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="580" spans="1:29">
+    <row r="580" spans="1:29" hidden="1">
       <c r="A580">
         <v>579</v>
       </c>
@@ -61876,7 +61891,7 @@
         <v>76</v>
       </c>
       <c r="Y580" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z580" t="s">
         <v>78</v>
@@ -61891,7 +61906,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="581" spans="1:29">
+    <row r="581" spans="1:29" hidden="1">
       <c r="A581">
         <v>580</v>
       </c>
@@ -62069,7 +62084,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="583" spans="1:29">
+    <row r="583" spans="1:29" hidden="1">
       <c r="A583">
         <v>582</v>
       </c>
@@ -62158,7 +62173,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="584" spans="1:29">
+    <row r="584" spans="1:29" hidden="1">
       <c r="A584">
         <v>583</v>
       </c>
@@ -62232,7 +62247,7 @@
         <v>76</v>
       </c>
       <c r="Y584" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z584" t="s">
         <v>78</v>
@@ -62247,7 +62262,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="585" spans="1:29">
+    <row r="585" spans="1:29" hidden="1">
       <c r="A585">
         <v>584</v>
       </c>
@@ -62425,7 +62440,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="587" spans="1:29">
+    <row r="587" spans="1:29" hidden="1">
       <c r="A587">
         <v>586</v>
       </c>
@@ -62514,7 +62529,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="588" spans="1:29">
+    <row r="588" spans="1:29" hidden="1">
       <c r="A588">
         <v>587</v>
       </c>
@@ -62603,7 +62618,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="589" spans="1:29">
+    <row r="589" spans="1:29" hidden="1">
       <c r="A589">
         <v>588</v>
       </c>
@@ -62781,7 +62796,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="591" spans="1:29">
+    <row r="591" spans="1:29" hidden="1">
       <c r="A591">
         <v>590</v>
       </c>
@@ -62870,7 +62885,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="592" spans="1:29">
+    <row r="592" spans="1:29" hidden="1">
       <c r="A592">
         <v>591</v>
       </c>
@@ -62944,7 +62959,7 @@
         <v>76</v>
       </c>
       <c r="Y592" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z592" t="s">
         <v>78</v>
@@ -62959,7 +62974,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="593" spans="1:29">
+    <row r="593" spans="1:29" hidden="1">
       <c r="A593">
         <v>592</v>
       </c>
@@ -63048,7 +63063,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="594" spans="1:29">
+    <row r="594" spans="1:29" hidden="1">
       <c r="A594">
         <v>593</v>
       </c>
@@ -63137,7 +63152,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="595" spans="1:29">
+    <row r="595" spans="1:29" hidden="1">
       <c r="A595">
         <v>594</v>
       </c>
@@ -63226,7 +63241,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="596" spans="1:29">
+    <row r="596" spans="1:29" hidden="1">
       <c r="A596">
         <v>595</v>
       </c>
@@ -63300,7 +63315,7 @@
         <v>76</v>
       </c>
       <c r="Y596" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z596" t="s">
         <v>78</v>
@@ -63315,7 +63330,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="597" spans="1:29">
+    <row r="597" spans="1:29" hidden="1">
       <c r="A597">
         <v>596</v>
       </c>
@@ -63493,7 +63508,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="599" spans="1:29">
+    <row r="599" spans="1:29" hidden="1">
       <c r="A599">
         <v>598</v>
       </c>
@@ -63582,7 +63597,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="600" spans="1:29">
+    <row r="600" spans="1:29" hidden="1">
       <c r="A600">
         <v>599</v>
       </c>
@@ -63671,7 +63686,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="601" spans="1:29">
+    <row r="601" spans="1:29" hidden="1">
       <c r="A601">
         <v>600</v>
       </c>
@@ -63849,7 +63864,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="603" spans="1:29">
+    <row r="603" spans="1:29" hidden="1">
       <c r="A603">
         <v>602</v>
       </c>
@@ -63938,7 +63953,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="604" spans="1:29">
+    <row r="604" spans="1:29" hidden="1">
       <c r="A604">
         <v>603</v>
       </c>
@@ -64012,7 +64027,7 @@
         <v>76</v>
       </c>
       <c r="Y604" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z604" t="s">
         <v>78</v>
@@ -64027,7 +64042,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="605" spans="1:29">
+    <row r="605" spans="1:29" hidden="1">
       <c r="A605">
         <v>604</v>
       </c>
@@ -64116,7 +64131,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="606" spans="1:29">
+    <row r="606" spans="1:29" hidden="1">
       <c r="A606">
         <v>605</v>
       </c>
@@ -64205,7 +64220,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="607" spans="1:29">
+    <row r="607" spans="1:29" hidden="1">
       <c r="A607">
         <v>606</v>
       </c>
@@ -64294,7 +64309,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="608" spans="1:29">
+    <row r="608" spans="1:29" hidden="1">
       <c r="A608">
         <v>607</v>
       </c>
@@ -64368,7 +64383,7 @@
         <v>76</v>
       </c>
       <c r="Y608" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z608" t="s">
         <v>78</v>
@@ -64383,7 +64398,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="609" spans="1:29">
+    <row r="609" spans="1:29" hidden="1">
       <c r="A609">
         <v>608</v>
       </c>
@@ -64561,7 +64576,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="611" spans="1:29">
+    <row r="611" spans="1:29" hidden="1">
       <c r="A611">
         <v>610</v>
       </c>
@@ -64650,7 +64665,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="612" spans="1:29">
+    <row r="612" spans="1:29" hidden="1">
       <c r="A612">
         <v>611</v>
       </c>
@@ -64739,7 +64754,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="613" spans="1:29">
+    <row r="613" spans="1:29" hidden="1">
       <c r="A613">
         <v>612</v>
       </c>
@@ -64917,7 +64932,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="615" spans="1:29">
+    <row r="615" spans="1:29" hidden="1">
       <c r="A615">
         <v>614</v>
       </c>
@@ -65006,7 +65021,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="616" spans="1:29">
+    <row r="616" spans="1:29" hidden="1">
       <c r="A616">
         <v>615</v>
       </c>
@@ -65080,7 +65095,7 @@
         <v>76</v>
       </c>
       <c r="Y616" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z616" t="s">
         <v>78</v>
@@ -65095,7 +65110,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="617" spans="1:29">
+    <row r="617" spans="1:29" hidden="1">
       <c r="A617">
         <v>616</v>
       </c>
@@ -65184,7 +65199,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="618" spans="1:29">
+    <row r="618" spans="1:29" hidden="1">
       <c r="A618">
         <v>617</v>
       </c>
@@ -65273,7 +65288,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="619" spans="1:29">
+    <row r="619" spans="1:29" hidden="1">
       <c r="A619">
         <v>618</v>
       </c>
@@ -65362,7 +65377,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="620" spans="1:29">
+    <row r="620" spans="1:29" hidden="1">
       <c r="A620">
         <v>619</v>
       </c>
@@ -65436,7 +65451,7 @@
         <v>76</v>
       </c>
       <c r="Y620" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z620" t="s">
         <v>78</v>
@@ -65451,7 +65466,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="621" spans="1:29">
+    <row r="621" spans="1:29" hidden="1">
       <c r="A621">
         <v>620</v>
       </c>
@@ -65629,7 +65644,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="623" spans="1:29">
+    <row r="623" spans="1:29" hidden="1">
       <c r="A623">
         <v>622</v>
       </c>
@@ -65718,7 +65733,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="624" spans="1:29">
+    <row r="624" spans="1:29" hidden="1">
       <c r="A624">
         <v>623</v>
       </c>
@@ -65807,7 +65822,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="625" spans="1:29">
+    <row r="625" spans="1:29" hidden="1">
       <c r="A625">
         <v>624</v>
       </c>
@@ -65985,7 +66000,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="627" spans="1:29">
+    <row r="627" spans="1:29" hidden="1">
       <c r="A627">
         <v>626</v>
       </c>
@@ -66074,7 +66089,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="628" spans="1:29">
+    <row r="628" spans="1:29" hidden="1">
       <c r="A628">
         <v>627</v>
       </c>
@@ -66148,7 +66163,7 @@
         <v>76</v>
       </c>
       <c r="Y628" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z628" t="s">
         <v>78</v>
@@ -66163,7 +66178,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="629" spans="1:29">
+    <row r="629" spans="1:29" hidden="1">
       <c r="A629">
         <v>628</v>
       </c>
@@ -66252,7 +66267,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="630" spans="1:29">
+    <row r="630" spans="1:29" hidden="1">
       <c r="A630">
         <v>629</v>
       </c>
@@ -66341,7 +66356,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="631" spans="1:29">
+    <row r="631" spans="1:29" hidden="1">
       <c r="A631">
         <v>630</v>
       </c>
@@ -66430,7 +66445,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="632" spans="1:29">
+    <row r="632" spans="1:29" hidden="1">
       <c r="A632">
         <v>631</v>
       </c>
@@ -66504,7 +66519,7 @@
         <v>76</v>
       </c>
       <c r="Y632" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z632" t="s">
         <v>78</v>
@@ -66519,7 +66534,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="633" spans="1:29">
+    <row r="633" spans="1:29" hidden="1">
       <c r="A633">
         <v>632</v>
       </c>
@@ -66697,7 +66712,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="635" spans="1:29">
+    <row r="635" spans="1:29" hidden="1">
       <c r="A635">
         <v>634</v>
       </c>
@@ -66786,7 +66801,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="636" spans="1:29">
+    <row r="636" spans="1:29" hidden="1">
       <c r="A636">
         <v>635</v>
       </c>
@@ -66875,7 +66890,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="637" spans="1:29">
+    <row r="637" spans="1:29" hidden="1">
       <c r="A637">
         <v>636</v>
       </c>
@@ -67053,7 +67068,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="639" spans="1:29">
+    <row r="639" spans="1:29" hidden="1">
       <c r="A639">
         <v>638</v>
       </c>
@@ -67142,7 +67157,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="640" spans="1:29">
+    <row r="640" spans="1:29" hidden="1">
       <c r="A640">
         <v>639</v>
       </c>
@@ -67216,7 +67231,7 @@
         <v>76</v>
       </c>
       <c r="Y640" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z640" t="s">
         <v>78</v>
@@ -67231,7 +67246,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="641" spans="1:29">
+    <row r="641" spans="1:29" hidden="1">
       <c r="A641">
         <v>640</v>
       </c>
@@ -67320,7 +67335,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="642" spans="1:29">
+    <row r="642" spans="1:29" hidden="1">
       <c r="A642">
         <v>641</v>
       </c>
@@ -67409,7 +67424,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="643" spans="1:29">
+    <row r="643" spans="1:29" hidden="1">
       <c r="A643">
         <v>642</v>
       </c>
@@ -67498,7 +67513,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="644" spans="1:29">
+    <row r="644" spans="1:29" hidden="1">
       <c r="A644">
         <v>643</v>
       </c>
@@ -67572,7 +67587,7 @@
         <v>76</v>
       </c>
       <c r="Y644" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z644" t="s">
         <v>78</v>
@@ -67587,7 +67602,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="645" spans="1:29">
+    <row r="645" spans="1:29" hidden="1">
       <c r="A645">
         <v>644</v>
       </c>
@@ -67765,7 +67780,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="647" spans="1:29">
+    <row r="647" spans="1:29" hidden="1">
       <c r="A647">
         <v>646</v>
       </c>
@@ -67854,7 +67869,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="648" spans="1:29">
+    <row r="648" spans="1:29" hidden="1">
       <c r="A648">
         <v>647</v>
       </c>
@@ -67943,7 +67958,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="649" spans="1:29">
+    <row r="649" spans="1:29" hidden="1">
       <c r="A649">
         <v>648</v>
       </c>
@@ -68121,7 +68136,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="651" spans="1:29">
+    <row r="651" spans="1:29" hidden="1">
       <c r="A651">
         <v>650</v>
       </c>
@@ -68210,7 +68225,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="652" spans="1:29">
+    <row r="652" spans="1:29" hidden="1">
       <c r="A652">
         <v>651</v>
       </c>
@@ -68284,7 +68299,7 @@
         <v>76</v>
       </c>
       <c r="Y652" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z652" t="s">
         <v>78</v>
@@ -68299,7 +68314,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="653" spans="1:29">
+    <row r="653" spans="1:29" hidden="1">
       <c r="A653">
         <v>652</v>
       </c>
@@ -68388,7 +68403,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="654" spans="1:29">
+    <row r="654" spans="1:29" hidden="1">
       <c r="A654">
         <v>653</v>
       </c>
@@ -68477,7 +68492,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="655" spans="1:29">
+    <row r="655" spans="1:29" hidden="1">
       <c r="A655">
         <v>654</v>
       </c>
@@ -68566,7 +68581,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="656" spans="1:29">
+    <row r="656" spans="1:29" hidden="1">
       <c r="A656">
         <v>655</v>
       </c>
@@ -68640,7 +68655,7 @@
         <v>76</v>
       </c>
       <c r="Y656" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z656" t="s">
         <v>78</v>
@@ -68655,7 +68670,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="657" spans="1:29">
+    <row r="657" spans="1:29" hidden="1">
       <c r="A657">
         <v>656</v>
       </c>
@@ -68827,13 +68842,13 @@
         <v>46211</v>
       </c>
       <c r="AB658" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC658" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="659" spans="1:29">
+    <row r="659" spans="1:29" hidden="1">
       <c r="A659">
         <v>658</v>
       </c>
@@ -68907,7 +68922,7 @@
         <v>76</v>
       </c>
       <c r="Y659" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z659" t="s">
         <v>78</v>
@@ -68922,7 +68937,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="660" spans="1:29">
+    <row r="660" spans="1:29" hidden="1">
       <c r="A660">
         <v>659</v>
       </c>
@@ -68996,7 +69011,7 @@
         <v>76</v>
       </c>
       <c r="Y660" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z660" t="s">
         <v>78</v>
@@ -69011,7 +69026,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="661" spans="1:29">
+    <row r="661" spans="1:29" hidden="1">
       <c r="A661">
         <v>660</v>
       </c>
@@ -69183,13 +69198,13 @@
         <v>46214</v>
       </c>
       <c r="AB662" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC662" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="663" spans="1:29">
+    <row r="663" spans="1:29" hidden="1">
       <c r="A663">
         <v>662</v>
       </c>
@@ -69278,7 +69293,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="664" spans="1:29">
+    <row r="664" spans="1:29" hidden="1">
       <c r="A664">
         <v>663</v>
       </c>
@@ -69352,7 +69367,7 @@
         <v>76</v>
       </c>
       <c r="Y664" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z664" t="s">
         <v>78</v>
@@ -69545,7 +69560,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="667" spans="1:29">
+    <row r="667" spans="1:29" hidden="1">
       <c r="A667">
         <v>666</v>
       </c>
@@ -69634,7 +69649,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="668" spans="1:29">
+    <row r="668" spans="1:29" hidden="1">
       <c r="A668">
         <v>667</v>
       </c>
@@ -69708,7 +69723,7 @@
         <v>76</v>
       </c>
       <c r="Y668" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z668" t="s">
         <v>78</v>
@@ -69723,7 +69738,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="669" spans="1:29">
+    <row r="669" spans="1:29" hidden="1">
       <c r="A669">
         <v>668</v>
       </c>
@@ -69901,7 +69916,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="671" spans="1:29">
+    <row r="671" spans="1:29" hidden="1">
       <c r="A671">
         <v>670</v>
       </c>
@@ -69975,7 +69990,7 @@
         <v>76</v>
       </c>
       <c r="Y671" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z671" t="s">
         <v>78</v>
@@ -69990,7 +70005,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="672" spans="1:29">
+    <row r="672" spans="1:29" hidden="1">
       <c r="A672">
         <v>671</v>
       </c>
@@ -70064,7 +70079,7 @@
         <v>76</v>
       </c>
       <c r="Y672" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z672" t="s">
         <v>78</v>
@@ -70079,7 +70094,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="673" spans="1:29">
+    <row r="673" spans="1:29" hidden="1">
       <c r="A673">
         <v>672</v>
       </c>
@@ -70257,7 +70272,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="675" spans="1:29">
+    <row r="675" spans="1:29" hidden="1">
       <c r="A675">
         <v>674</v>
       </c>
@@ -70346,7 +70361,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="676" spans="1:29">
+    <row r="676" spans="1:29" hidden="1">
       <c r="A676">
         <v>675</v>
       </c>
@@ -70420,7 +70435,7 @@
         <v>76</v>
       </c>
       <c r="Y676" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z676" t="s">
         <v>78</v>
@@ -70613,7 +70628,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="679" spans="1:29">
+    <row r="679" spans="1:29" hidden="1">
       <c r="A679">
         <v>678</v>
       </c>
@@ -70702,7 +70717,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="680" spans="1:29">
+    <row r="680" spans="1:29" hidden="1">
       <c r="A680">
         <v>679</v>
       </c>
@@ -70776,7 +70791,7 @@
         <v>76</v>
       </c>
       <c r="Y680" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z680" t="s">
         <v>78</v>
@@ -70791,7 +70806,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="681" spans="1:29">
+    <row r="681" spans="1:29" hidden="1">
       <c r="A681">
         <v>680</v>
       </c>
@@ -70969,7 +70984,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="683" spans="1:29">
+    <row r="683" spans="1:29" hidden="1">
       <c r="A683">
         <v>682</v>
       </c>
@@ -71043,7 +71058,7 @@
         <v>76</v>
       </c>
       <c r="Y683" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z683" t="s">
         <v>78</v>
@@ -71058,7 +71073,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="684" spans="1:29">
+    <row r="684" spans="1:29" hidden="1">
       <c r="A684">
         <v>683</v>
       </c>
@@ -71132,7 +71147,7 @@
         <v>76</v>
       </c>
       <c r="Y684" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z684" t="s">
         <v>78</v>
@@ -71147,7 +71162,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="685" spans="1:29">
+    <row r="685" spans="1:29" hidden="1">
       <c r="A685">
         <v>684</v>
       </c>
@@ -71325,7 +71340,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="687" spans="1:29">
+    <row r="687" spans="1:29" hidden="1">
       <c r="A687">
         <v>686</v>
       </c>
@@ -71414,7 +71429,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="688" spans="1:29">
+    <row r="688" spans="1:29" hidden="1">
       <c r="A688">
         <v>687</v>
       </c>
@@ -71488,7 +71503,7 @@
         <v>76</v>
       </c>
       <c r="Y688" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z688" t="s">
         <v>78</v>
@@ -71681,7 +71696,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="691" spans="1:29">
+    <row r="691" spans="1:29" hidden="1">
       <c r="A691">
         <v>690</v>
       </c>
@@ -71770,7 +71785,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="692" spans="1:29">
+    <row r="692" spans="1:29" hidden="1">
       <c r="A692">
         <v>691</v>
       </c>
@@ -71844,7 +71859,7 @@
         <v>76</v>
       </c>
       <c r="Y692" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z692" t="s">
         <v>78</v>
@@ -71859,7 +71874,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="693" spans="1:29">
+    <row r="693" spans="1:29" hidden="1">
       <c r="A693">
         <v>692</v>
       </c>
@@ -72037,7 +72052,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="695" spans="1:29">
+    <row r="695" spans="1:29" hidden="1">
       <c r="A695">
         <v>694</v>
       </c>
@@ -72111,7 +72126,7 @@
         <v>76</v>
       </c>
       <c r="Y695" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z695" t="s">
         <v>78</v>
@@ -72126,7 +72141,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="696" spans="1:29">
+    <row r="696" spans="1:29" hidden="1">
       <c r="A696">
         <v>695</v>
       </c>
@@ -72200,7 +72215,7 @@
         <v>76</v>
       </c>
       <c r="Y696" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z696" t="s">
         <v>78</v>
@@ -72215,7 +72230,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="697" spans="1:29">
+    <row r="697" spans="1:29" hidden="1">
       <c r="A697">
         <v>696</v>
       </c>
@@ -72393,7 +72408,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="699" spans="1:29">
+    <row r="699" spans="1:29" hidden="1">
       <c r="A699">
         <v>698</v>
       </c>
@@ -72482,7 +72497,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="700" spans="1:29">
+    <row r="700" spans="1:29" hidden="1">
       <c r="A700">
         <v>699</v>
       </c>
@@ -72556,7 +72571,7 @@
         <v>76</v>
       </c>
       <c r="Y700" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z700" t="s">
         <v>78</v>
@@ -72749,7 +72764,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="703" spans="1:29">
+    <row r="703" spans="1:29" hidden="1">
       <c r="A703">
         <v>702</v>
       </c>
@@ -72838,7 +72853,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="704" spans="1:29">
+    <row r="704" spans="1:29" hidden="1">
       <c r="A704">
         <v>703</v>
       </c>
@@ -72912,7 +72927,7 @@
         <v>76</v>
       </c>
       <c r="Y704" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z704" t="s">
         <v>78</v>
@@ -72927,7 +72942,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="705" spans="1:29">
+    <row r="705" spans="1:29" hidden="1">
       <c r="A705">
         <v>704</v>
       </c>
@@ -73105,7 +73120,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="707" spans="1:29">
+    <row r="707" spans="1:29" hidden="1">
       <c r="A707">
         <v>706</v>
       </c>
@@ -73179,7 +73194,7 @@
         <v>76</v>
       </c>
       <c r="Y707" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z707" t="s">
         <v>78</v>
@@ -73194,7 +73209,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="708" spans="1:29">
+    <row r="708" spans="1:29" hidden="1">
       <c r="A708">
         <v>707</v>
       </c>
@@ -73268,7 +73283,7 @@
         <v>76</v>
       </c>
       <c r="Y708" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z708" t="s">
         <v>78</v>
@@ -73283,7 +73298,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="709" spans="1:29">
+    <row r="709" spans="1:29" hidden="1">
       <c r="A709">
         <v>708</v>
       </c>
@@ -73461,7 +73476,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="711" spans="1:29">
+    <row r="711" spans="1:29" hidden="1">
       <c r="A711">
         <v>710</v>
       </c>
@@ -73550,7 +73565,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="712" spans="1:29">
+    <row r="712" spans="1:29" hidden="1">
       <c r="A712">
         <v>711</v>
       </c>
@@ -73624,7 +73639,7 @@
         <v>76</v>
       </c>
       <c r="Y712" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z712" t="s">
         <v>78</v>
@@ -73817,7 +73832,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="715" spans="1:29">
+    <row r="715" spans="1:29" hidden="1">
       <c r="A715">
         <v>714</v>
       </c>
@@ -73906,7 +73921,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="716" spans="1:29">
+    <row r="716" spans="1:29" hidden="1">
       <c r="A716">
         <v>715</v>
       </c>
@@ -73980,7 +73995,7 @@
         <v>76</v>
       </c>
       <c r="Y716" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z716" t="s">
         <v>78</v>
@@ -73995,7 +74010,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="717" spans="1:29">
+    <row r="717" spans="1:29" hidden="1">
       <c r="A717">
         <v>716</v>
       </c>
@@ -74167,13 +74182,13 @@
         <v>46261</v>
       </c>
       <c r="AB718" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC718" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="719" spans="1:29">
+    <row r="719" spans="1:29" hidden="1">
       <c r="A719">
         <v>718</v>
       </c>
@@ -74247,7 +74262,7 @@
         <v>76</v>
       </c>
       <c r="Y719" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z719" t="s">
         <v>78</v>
@@ -74262,7 +74277,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="720" spans="1:29">
+    <row r="720" spans="1:29" hidden="1">
       <c r="A720">
         <v>719</v>
       </c>
@@ -74336,7 +74351,7 @@
         <v>76</v>
       </c>
       <c r="Y720" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z720" t="s">
         <v>78</v>
@@ -74351,7 +74366,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="721" spans="1:29">
+    <row r="721" spans="1:29" hidden="1">
       <c r="A721">
         <v>720</v>
       </c>
@@ -74529,7 +74544,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="723" spans="1:29">
+    <row r="723" spans="1:29" hidden="1">
       <c r="A723">
         <v>722</v>
       </c>
@@ -74618,7 +74633,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="724" spans="1:29">
+    <row r="724" spans="1:29" hidden="1">
       <c r="A724">
         <v>723</v>
       </c>
@@ -74692,7 +74707,7 @@
         <v>76</v>
       </c>
       <c r="Y724" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z724" t="s">
         <v>78</v>
@@ -74885,7 +74900,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="727" spans="1:29">
+    <row r="727" spans="1:29" hidden="1">
       <c r="A727">
         <v>726</v>
       </c>
@@ -74974,7 +74989,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="728" spans="1:29">
+    <row r="728" spans="1:29" hidden="1">
       <c r="A728">
         <v>727</v>
       </c>
@@ -75048,7 +75063,7 @@
         <v>76</v>
       </c>
       <c r="Y728" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z728" t="s">
         <v>78</v>
@@ -75063,7 +75078,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="729" spans="1:29">
+    <row r="729" spans="1:29" hidden="1">
       <c r="A729">
         <v>728</v>
       </c>
@@ -75241,7 +75256,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="731" spans="1:29">
+    <row r="731" spans="1:29" hidden="1">
       <c r="A731">
         <v>730</v>
       </c>
@@ -75315,7 +75330,7 @@
         <v>76</v>
       </c>
       <c r="Y731" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z731" t="s">
         <v>78</v>
@@ -75330,7 +75345,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="732" spans="1:29">
+    <row r="732" spans="1:29" hidden="1">
       <c r="A732">
         <v>731</v>
       </c>
@@ -75404,7 +75419,7 @@
         <v>76</v>
       </c>
       <c r="Y732" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z732" t="s">
         <v>78</v>
@@ -75419,7 +75434,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="733" spans="1:29">
+    <row r="733" spans="1:29" hidden="1">
       <c r="A733">
         <v>732</v>
       </c>
@@ -75597,7 +75612,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="735" spans="1:29">
+    <row r="735" spans="1:29" hidden="1">
       <c r="A735">
         <v>734</v>
       </c>
@@ -75686,7 +75701,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="736" spans="1:29">
+    <row r="736" spans="1:29" hidden="1">
       <c r="A736">
         <v>735</v>
       </c>
@@ -75760,7 +75775,7 @@
         <v>76</v>
       </c>
       <c r="Y736" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z736" t="s">
         <v>78</v>
@@ -75858,7 +75873,7 @@
         <v>46274</v>
       </c>
       <c r="AB737" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC737" t="s">
         <v>46</v>
@@ -75947,13 +75962,13 @@
         <v>46277</v>
       </c>
       <c r="AB738" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC738" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="739" spans="1:29">
+    <row r="739" spans="1:29" hidden="1">
       <c r="A739">
         <v>738</v>
       </c>
@@ -76042,7 +76057,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="740" spans="1:29">
+    <row r="740" spans="1:29" hidden="1">
       <c r="A740">
         <v>739</v>
       </c>
@@ -76116,7 +76131,7 @@
         <v>76</v>
       </c>
       <c r="Y740" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z740" t="s">
         <v>78</v>
@@ -76131,7 +76146,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="741" spans="1:29">
+    <row r="741" spans="1:29" hidden="1">
       <c r="A741">
         <v>740</v>
       </c>
@@ -76303,13 +76318,13 @@
         <v>46277</v>
       </c>
       <c r="AB742" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC742" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="743" spans="1:29">
+    <row r="743" spans="1:29" hidden="1">
       <c r="A743">
         <v>742</v>
       </c>
@@ -76383,7 +76398,7 @@
         <v>76</v>
       </c>
       <c r="Y743" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z743" t="s">
         <v>78</v>
@@ -76398,7 +76413,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="744" spans="1:29">
+    <row r="744" spans="1:29" hidden="1">
       <c r="A744">
         <v>743</v>
       </c>
@@ -76472,7 +76487,7 @@
         <v>76</v>
       </c>
       <c r="Y744" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z744" t="s">
         <v>78</v>
@@ -76487,7 +76502,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="745" spans="1:29">
+    <row r="745" spans="1:29" hidden="1">
       <c r="A745">
         <v>744</v>
       </c>
@@ -76665,7 +76680,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="747" spans="1:29">
+    <row r="747" spans="1:29" hidden="1">
       <c r="A747">
         <v>746</v>
       </c>
@@ -76754,7 +76769,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="748" spans="1:29">
+    <row r="748" spans="1:29" hidden="1">
       <c r="A748">
         <v>747</v>
       </c>
@@ -76828,7 +76843,7 @@
         <v>76</v>
       </c>
       <c r="Y748" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z748" t="s">
         <v>78</v>
@@ -77021,7 +77036,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="751" spans="1:29">
+    <row r="751" spans="1:29" hidden="1">
       <c r="A751">
         <v>750</v>
       </c>
@@ -77110,7 +77125,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="752" spans="1:29">
+    <row r="752" spans="1:29" hidden="1">
       <c r="A752">
         <v>751</v>
       </c>
@@ -77184,7 +77199,7 @@
         <v>76</v>
       </c>
       <c r="Y752" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z752" t="s">
         <v>78</v>
@@ -77199,7 +77214,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="753" spans="1:29">
+    <row r="753" spans="1:29" hidden="1">
       <c r="A753">
         <v>752</v>
       </c>
@@ -77377,7 +77392,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="755" spans="1:29">
+    <row r="755" spans="1:29" hidden="1">
       <c r="A755">
         <v>754</v>
       </c>
@@ -77451,7 +77466,7 @@
         <v>76</v>
       </c>
       <c r="Y755" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z755" t="s">
         <v>78</v>
@@ -77466,7 +77481,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="756" spans="1:29">
+    <row r="756" spans="1:29" hidden="1">
       <c r="A756">
         <v>755</v>
       </c>
@@ -77540,7 +77555,7 @@
         <v>76</v>
       </c>
       <c r="Y756" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z756" t="s">
         <v>78</v>
@@ -77555,7 +77570,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="757" spans="1:29">
+    <row r="757" spans="1:29" hidden="1">
       <c r="A757">
         <v>756</v>
       </c>
@@ -77733,7 +77748,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="759" spans="1:29">
+    <row r="759" spans="1:29" hidden="1">
       <c r="A759">
         <v>758</v>
       </c>
@@ -77822,7 +77837,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="760" spans="1:29">
+    <row r="760" spans="1:29" hidden="1">
       <c r="A760">
         <v>759</v>
       </c>
@@ -77896,7 +77911,7 @@
         <v>76</v>
       </c>
       <c r="Y760" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z760" t="s">
         <v>78</v>
@@ -78089,7 +78104,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="763" spans="1:29">
+    <row r="763" spans="1:29" hidden="1">
       <c r="A763">
         <v>762</v>
       </c>
@@ -78178,7 +78193,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="764" spans="1:29">
+    <row r="764" spans="1:29" hidden="1">
       <c r="A764">
         <v>763</v>
       </c>
@@ -78252,7 +78267,7 @@
         <v>76</v>
       </c>
       <c r="Y764" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z764" t="s">
         <v>78</v>
@@ -78267,7 +78282,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="765" spans="1:29">
+    <row r="765" spans="1:29" hidden="1">
       <c r="A765">
         <v>764</v>
       </c>
@@ -78445,7 +78460,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="767" spans="1:29">
+    <row r="767" spans="1:29" hidden="1">
       <c r="A767">
         <v>766</v>
       </c>
@@ -78534,7 +78549,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="768" spans="1:29">
+    <row r="768" spans="1:29" hidden="1">
       <c r="A768">
         <v>767</v>
       </c>
@@ -78608,7 +78623,7 @@
         <v>76</v>
       </c>
       <c r="Y768" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z768" t="s">
         <v>78</v>
@@ -78623,7 +78638,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="769" spans="1:29">
+    <row r="769" spans="1:29" hidden="1">
       <c r="A769">
         <v>768</v>
       </c>
@@ -78801,7 +78816,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="771" spans="1:29">
+    <row r="771" spans="1:29" hidden="1">
       <c r="A771">
         <v>770</v>
       </c>
@@ -78875,7 +78890,7 @@
         <v>76</v>
       </c>
       <c r="Y771" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z771" t="s">
         <v>78</v>
@@ -78890,7 +78905,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="772" spans="1:29">
+    <row r="772" spans="1:29" hidden="1">
       <c r="A772">
         <v>771</v>
       </c>
@@ -78964,7 +78979,7 @@
         <v>76</v>
       </c>
       <c r="Y772" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z772" t="s">
         <v>78</v>
@@ -78979,7 +78994,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="773" spans="1:29">
+    <row r="773" spans="1:29" hidden="1">
       <c r="A773">
         <v>772</v>
       </c>
@@ -79157,7 +79172,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="775" spans="1:29">
+    <row r="775" spans="1:29" hidden="1">
       <c r="A775">
         <v>774</v>
       </c>
@@ -79246,7 +79261,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="776" spans="1:29">
+    <row r="776" spans="1:29" hidden="1">
       <c r="A776">
         <v>775</v>
       </c>
@@ -79320,7 +79335,7 @@
         <v>76</v>
       </c>
       <c r="Y776" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z776" t="s">
         <v>78</v>
@@ -79513,7 +79528,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="779" spans="1:29">
+    <row r="779" spans="1:29" hidden="1">
       <c r="A779">
         <v>778</v>
       </c>
@@ -79602,7 +79617,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="780" spans="1:29">
+    <row r="780" spans="1:29" hidden="1">
       <c r="A780">
         <v>779</v>
       </c>
@@ -79676,7 +79691,7 @@
         <v>76</v>
       </c>
       <c r="Y780" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z780" t="s">
         <v>78</v>
@@ -79691,7 +79706,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="781" spans="1:29">
+    <row r="781" spans="1:29" hidden="1">
       <c r="A781">
         <v>780</v>
       </c>
@@ -79869,7 +79884,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="783" spans="1:29">
+    <row r="783" spans="1:29" hidden="1">
       <c r="A783">
         <v>782</v>
       </c>
@@ -79943,7 +79958,7 @@
         <v>76</v>
       </c>
       <c r="Y783" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z783" t="s">
         <v>78</v>
@@ -79958,7 +79973,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="784" spans="1:29">
+    <row r="784" spans="1:29" hidden="1">
       <c r="A784">
         <v>783</v>
       </c>
@@ -80032,7 +80047,7 @@
         <v>76</v>
       </c>
       <c r="Y784" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z784" t="s">
         <v>78</v>
@@ -80047,7 +80062,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="785" spans="1:29">
+    <row r="785" spans="1:29" hidden="1">
       <c r="A785">
         <v>784</v>
       </c>
@@ -80225,7 +80240,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="787" spans="1:29">
+    <row r="787" spans="1:29" hidden="1">
       <c r="A787">
         <v>786</v>
       </c>
@@ -80314,7 +80329,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="788" spans="1:29">
+    <row r="788" spans="1:29" hidden="1">
       <c r="A788">
         <v>787</v>
       </c>
@@ -80388,7 +80403,7 @@
         <v>76</v>
       </c>
       <c r="Y788" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z788" t="s">
         <v>78</v>
@@ -80581,7 +80596,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="791" spans="1:29">
+    <row r="791" spans="1:29" hidden="1">
       <c r="A791">
         <v>790</v>
       </c>
@@ -80670,7 +80685,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="792" spans="1:29">
+    <row r="792" spans="1:29" hidden="1">
       <c r="A792">
         <v>791</v>
       </c>
@@ -80744,7 +80759,7 @@
         <v>76</v>
       </c>
       <c r="Y792" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z792" t="s">
         <v>78</v>
@@ -80759,7 +80774,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="793" spans="1:29">
+    <row r="793" spans="1:29" hidden="1">
       <c r="A793">
         <v>792</v>
       </c>
@@ -80931,13 +80946,13 @@
         <v>46325</v>
       </c>
       <c r="AB794" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC794" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="795" spans="1:29">
+    <row r="795" spans="1:29" hidden="1">
       <c r="A795">
         <v>794</v>
       </c>
@@ -81011,7 +81026,7 @@
         <v>76</v>
       </c>
       <c r="Y795" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z795" t="s">
         <v>78</v>
@@ -81026,7 +81041,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="796" spans="1:29">
+    <row r="796" spans="1:29" hidden="1">
       <c r="A796">
         <v>795</v>
       </c>
@@ -81100,7 +81115,7 @@
         <v>76</v>
       </c>
       <c r="Y796" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z796" t="s">
         <v>78</v>
@@ -81115,7 +81130,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="797" spans="1:29">
+    <row r="797" spans="1:29" hidden="1">
       <c r="A797">
         <v>796</v>
       </c>
@@ -81293,7 +81308,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="799" spans="1:29">
+    <row r="799" spans="1:29" hidden="1">
       <c r="A799">
         <v>798</v>
       </c>
@@ -81382,7 +81397,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="800" spans="1:29">
+    <row r="800" spans="1:29" hidden="1">
       <c r="A800">
         <v>799</v>
       </c>
@@ -81456,7 +81471,7 @@
         <v>76</v>
       </c>
       <c r="Y800" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z800" t="s">
         <v>78</v>
@@ -81649,7 +81664,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="803" spans="1:29">
+    <row r="803" spans="1:29" hidden="1">
       <c r="A803">
         <v>802</v>
       </c>
@@ -81738,7 +81753,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="804" spans="1:29">
+    <row r="804" spans="1:29" hidden="1">
       <c r="A804">
         <v>803</v>
       </c>
@@ -81812,7 +81827,7 @@
         <v>76</v>
       </c>
       <c r="Y804" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z804" t="s">
         <v>78</v>
@@ -81827,7 +81842,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="805" spans="1:29">
+    <row r="805" spans="1:29" hidden="1">
       <c r="A805">
         <v>804</v>
       </c>
@@ -82005,7 +82020,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="807" spans="1:29">
+    <row r="807" spans="1:29" hidden="1">
       <c r="A807">
         <v>806</v>
       </c>
@@ -82079,7 +82094,7 @@
         <v>76</v>
       </c>
       <c r="Y807" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z807" t="s">
         <v>78</v>
@@ -82094,7 +82109,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="808" spans="1:29">
+    <row r="808" spans="1:29" hidden="1">
       <c r="A808">
         <v>807</v>
       </c>
@@ -82168,7 +82183,7 @@
         <v>76</v>
       </c>
       <c r="Y808" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z808" t="s">
         <v>78</v>
@@ -82183,7 +82198,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="809" spans="1:29">
+    <row r="809" spans="1:29" hidden="1">
       <c r="A809">
         <v>808</v>
       </c>
@@ -82355,13 +82370,13 @@
         <v>46338</v>
       </c>
       <c r="AB810" t="s">
-        <v>45</v>
+        <v>2894</v>
       </c>
       <c r="AC810" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="811" spans="1:29">
+    <row r="811" spans="1:29" hidden="1">
       <c r="A811">
         <v>810</v>
       </c>
@@ -82450,7 +82465,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="812" spans="1:29">
+    <row r="812" spans="1:29" hidden="1">
       <c r="A812">
         <v>811</v>
       </c>
@@ -82524,7 +82539,7 @@
         <v>76</v>
       </c>
       <c r="Y812" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z812" t="s">
         <v>78</v>
@@ -82717,7 +82732,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="815" spans="1:29">
+    <row r="815" spans="1:29" hidden="1">
       <c r="A815">
         <v>814</v>
       </c>
@@ -82806,7 +82821,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="816" spans="1:29">
+    <row r="816" spans="1:29" hidden="1">
       <c r="A816">
         <v>815</v>
       </c>
@@ -82880,7 +82895,7 @@
         <v>76</v>
       </c>
       <c r="Y816" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z816" t="s">
         <v>78</v>
@@ -82895,7 +82910,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="817" spans="1:29">
+    <row r="817" spans="1:29" hidden="1">
       <c r="A817">
         <v>816</v>
       </c>
@@ -83073,7 +83088,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="819" spans="1:29">
+    <row r="819" spans="1:29" hidden="1">
       <c r="A819">
         <v>818</v>
       </c>
@@ -83147,7 +83162,7 @@
         <v>76</v>
       </c>
       <c r="Y819" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z819" t="s">
         <v>78</v>
@@ -83162,7 +83177,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="820" spans="1:29">
+    <row r="820" spans="1:29" hidden="1">
       <c r="A820">
         <v>819</v>
       </c>
@@ -83236,7 +83251,7 @@
         <v>76</v>
       </c>
       <c r="Y820" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z820" t="s">
         <v>78</v>
@@ -83251,7 +83266,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="821" spans="1:29">
+    <row r="821" spans="1:29" hidden="1">
       <c r="A821">
         <v>820</v>
       </c>
@@ -83429,7 +83444,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="823" spans="1:29">
+    <row r="823" spans="1:29" hidden="1">
       <c r="A823">
         <v>822</v>
       </c>
@@ -83518,7 +83533,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="824" spans="1:29">
+    <row r="824" spans="1:29" hidden="1">
       <c r="A824">
         <v>823</v>
       </c>
@@ -83592,7 +83607,7 @@
         <v>76</v>
       </c>
       <c r="Y824" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z824" t="s">
         <v>78</v>
@@ -83785,7 +83800,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="827" spans="1:29">
+    <row r="827" spans="1:29" hidden="1">
       <c r="A827">
         <v>826</v>
       </c>
@@ -83874,7 +83889,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="828" spans="1:29">
+    <row r="828" spans="1:29" hidden="1">
       <c r="A828">
         <v>827</v>
       </c>
@@ -83948,7 +83963,7 @@
         <v>76</v>
       </c>
       <c r="Y828" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z828" t="s">
         <v>78</v>
@@ -83963,7 +83978,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="829" spans="1:29">
+    <row r="829" spans="1:29" hidden="1">
       <c r="A829">
         <v>828</v>
       </c>
@@ -84141,7 +84156,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="831" spans="1:29">
+    <row r="831" spans="1:29" hidden="1">
       <c r="A831">
         <v>830</v>
       </c>
@@ -84215,7 +84230,7 @@
         <v>76</v>
       </c>
       <c r="Y831" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z831" t="s">
         <v>78</v>
@@ -84230,7 +84245,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="832" spans="1:29">
+    <row r="832" spans="1:29" hidden="1">
       <c r="A832">
         <v>831</v>
       </c>
@@ -84304,7 +84319,7 @@
         <v>76</v>
       </c>
       <c r="Y832" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z832" t="s">
         <v>78</v>
@@ -84319,7 +84334,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="833" spans="1:29">
+    <row r="833" spans="1:29" hidden="1">
       <c r="A833">
         <v>832</v>
       </c>
@@ -84497,7 +84512,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="835" spans="1:29">
+    <row r="835" spans="1:29" hidden="1">
       <c r="A835">
         <v>834</v>
       </c>
@@ -84586,7 +84601,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="836" spans="1:29">
+    <row r="836" spans="1:29" hidden="1">
       <c r="A836">
         <v>835</v>
       </c>
@@ -84660,7 +84675,7 @@
         <v>76</v>
       </c>
       <c r="Y836" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z836" t="s">
         <v>78</v>
@@ -84853,7 +84868,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="839" spans="1:29">
+    <row r="839" spans="1:29" hidden="1">
       <c r="A839">
         <v>838</v>
       </c>
@@ -84942,7 +84957,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="840" spans="1:29">
+    <row r="840" spans="1:29" hidden="1">
       <c r="A840">
         <v>839</v>
       </c>
@@ -85016,7 +85031,7 @@
         <v>76</v>
       </c>
       <c r="Y840" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z840" t="s">
         <v>78</v>
@@ -85031,7 +85046,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="841" spans="1:29">
+    <row r="841" spans="1:29" hidden="1">
       <c r="A841">
         <v>840</v>
       </c>
@@ -85120,7 +85135,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="842" spans="1:29">
+    <row r="842" spans="1:29" hidden="1">
       <c r="A842">
         <v>841</v>
       </c>
@@ -85209,7 +85224,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="843" spans="1:29">
+    <row r="843" spans="1:29" hidden="1">
       <c r="A843">
         <v>842</v>
       </c>
@@ -85298,7 +85313,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="844" spans="1:29">
+    <row r="844" spans="1:29" hidden="1">
       <c r="A844">
         <v>843</v>
       </c>
@@ -85372,7 +85387,7 @@
         <v>76</v>
       </c>
       <c r="Y844" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z844" t="s">
         <v>78</v>
@@ -85387,7 +85402,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="845" spans="1:29">
+    <row r="845" spans="1:29" hidden="1">
       <c r="A845">
         <v>844</v>
       </c>
@@ -85565,7 +85580,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="847" spans="1:29">
+    <row r="847" spans="1:29" hidden="1">
       <c r="A847">
         <v>846</v>
       </c>
@@ -85654,7 +85669,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="848" spans="1:29">
+    <row r="848" spans="1:29" hidden="1">
       <c r="A848">
         <v>847</v>
       </c>
@@ -85743,7 +85758,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="849" spans="1:29">
+    <row r="849" spans="1:29" hidden="1">
       <c r="A849">
         <v>848</v>
       </c>
@@ -85921,7 +85936,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="851" spans="1:29">
+    <row r="851" spans="1:29" hidden="1">
       <c r="A851">
         <v>850</v>
       </c>
@@ -86010,7 +86025,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="852" spans="1:29">
+    <row r="852" spans="1:29" hidden="1">
       <c r="A852">
         <v>851</v>
       </c>
@@ -86084,7 +86099,7 @@
         <v>76</v>
       </c>
       <c r="Y852" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z852" t="s">
         <v>78</v>
@@ -86099,7 +86114,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="853" spans="1:29">
+    <row r="853" spans="1:29" hidden="1">
       <c r="A853">
         <v>852</v>
       </c>
@@ -86188,7 +86203,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="854" spans="1:29">
+    <row r="854" spans="1:29" hidden="1">
       <c r="A854">
         <v>853</v>
       </c>
@@ -86277,7 +86292,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="855" spans="1:29">
+    <row r="855" spans="1:29" hidden="1">
       <c r="A855">
         <v>854</v>
       </c>
@@ -86366,7 +86381,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="856" spans="1:29">
+    <row r="856" spans="1:29" hidden="1">
       <c r="A856">
         <v>855</v>
       </c>
@@ -86440,7 +86455,7 @@
         <v>76</v>
       </c>
       <c r="Y856" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z856" t="s">
         <v>78</v>
@@ -86455,7 +86470,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="857" spans="1:29">
+    <row r="857" spans="1:29" hidden="1">
       <c r="A857">
         <v>856</v>
       </c>
@@ -86633,7 +86648,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="859" spans="1:29">
+    <row r="859" spans="1:29" hidden="1">
       <c r="A859">
         <v>858</v>
       </c>
@@ -86722,7 +86737,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="860" spans="1:29">
+    <row r="860" spans="1:29" hidden="1">
       <c r="A860">
         <v>859</v>
       </c>
@@ -86811,7 +86826,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="861" spans="1:29">
+    <row r="861" spans="1:29" hidden="1">
       <c r="A861">
         <v>860</v>
       </c>
@@ -86989,7 +87004,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="863" spans="1:29">
+    <row r="863" spans="1:29" hidden="1">
       <c r="A863">
         <v>862</v>
       </c>
@@ -87078,7 +87093,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="864" spans="1:29">
+    <row r="864" spans="1:29" hidden="1">
       <c r="A864">
         <v>863</v>
       </c>
@@ -87152,7 +87167,7 @@
         <v>76</v>
       </c>
       <c r="Y864" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z864" t="s">
         <v>78</v>
@@ -87167,7 +87182,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="865" spans="1:29">
+    <row r="865" spans="1:29" hidden="1">
       <c r="A865">
         <v>864</v>
       </c>
@@ -87256,7 +87271,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="866" spans="1:29">
+    <row r="866" spans="1:29" hidden="1">
       <c r="A866">
         <v>865</v>
       </c>
@@ -87345,7 +87360,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="867" spans="1:29">
+    <row r="867" spans="1:29" hidden="1">
       <c r="A867">
         <v>866</v>
       </c>
@@ -87434,7 +87449,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="868" spans="1:29">
+    <row r="868" spans="1:29" hidden="1">
       <c r="A868">
         <v>867</v>
       </c>
@@ -87508,7 +87523,7 @@
         <v>76</v>
       </c>
       <c r="Y868" t="s">
-        <v>77</v>
+        <v>3014</v>
       </c>
       <c r="Z868" t="s">
         <v>78</v>
@@ -87523,7 +87538,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="869" spans="1:29">
+    <row r="869" spans="1:29" hidden="1">
       <c r="A869">
         <v>868</v>
       </c>
@@ -87701,7 +87716,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="871" spans="1:29">
+    <row r="871" spans="1:29" hidden="1">
       <c r="A871">
         <v>870</v>
       </c>
@@ -87790,7 +87805,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="872" spans="1:29">
+    <row r="872" spans="1:29" hidden="1">
       <c r="A872">
         <v>871</v>
       </c>
@@ -87879,7 +87894,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="873" spans="1:29">
+    <row r="873" spans="1:29" hidden="1">
       <c r="A873">
         <v>872</v>
       </c>
@@ -88057,7 +88072,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="875" spans="1:29">
+    <row r="875" spans="1:29" hidden="1">
       <c r="A875">
         <v>874</v>
       </c>
